--- a/data/Brienz (BE)/investment_decision/aggregated_investment_decision.xlsx
+++ b/data/Brienz (BE)/investment_decision/aggregated_investment_decision.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K221"/>
+  <dimension ref="A1:K226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,32 +455,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>scen_all_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>scen_all_candidate_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>scen_cp_dr_invested_available_unit</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_candidate_unit</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -499,25 +499,25 @@
         <v>46023</v>
       </c>
       <c r="C2" t="n">
-        <v>1039.280146280126</v>
+        <v>329.9777417924758</v>
       </c>
       <c r="D2" t="n">
         <v>1079589.365674657</v>
       </c>
       <c r="E2" t="n">
-        <v>1211.669749583471</v>
+        <v>333.8311141307964</v>
       </c>
       <c r="F2" t="n">
         <v>1079589.365674657</v>
       </c>
       <c r="G2" t="n">
-        <v>1166.126205953542</v>
+        <v>332.4917695091981</v>
       </c>
       <c r="H2" t="n">
         <v>1079589.365674657</v>
       </c>
       <c r="I2" t="n">
-        <v>1040.240664615408</v>
+        <v>333.5682069310309</v>
       </c>
       <c r="J2" t="n">
         <v>1079589.365674657</v>
@@ -536,25 +536,25 @@
         <v>47849</v>
       </c>
       <c r="C3" t="n">
-        <v>2063.065817127664</v>
+        <v>1891.725451024016</v>
       </c>
       <c r="D3" t="n">
         <v>1079589.365674657</v>
       </c>
       <c r="E3" t="n">
-        <v>2387.721948615551</v>
+        <v>2204.732604831165</v>
       </c>
       <c r="F3" t="n">
         <v>1079589.365674657</v>
       </c>
       <c r="G3" t="n">
-        <v>2355.687457171771</v>
+        <v>1639.036748083015</v>
       </c>
       <c r="H3" t="n">
         <v>1079589.365674657</v>
       </c>
       <c r="I3" t="n">
-        <v>2020.501255919707</v>
+        <v>2168.409729169251</v>
       </c>
       <c r="J3" t="n">
         <v>1079589.365674657</v>
@@ -573,25 +573,25 @@
         <v>49675</v>
       </c>
       <c r="C4" t="n">
-        <v>5073.772077773051</v>
+        <v>3033.522730866931</v>
       </c>
       <c r="D4" t="n">
         <v>1079589.365674657</v>
       </c>
       <c r="E4" t="n">
-        <v>5317.738791682751</v>
+        <v>2991.467869297489</v>
       </c>
       <c r="F4" t="n">
         <v>1079589.365674657</v>
       </c>
       <c r="G4" t="n">
-        <v>4820.147555300238</v>
+        <v>2960.599113899077</v>
       </c>
       <c r="H4" t="n">
         <v>1079589.365674657</v>
       </c>
       <c r="I4" t="n">
-        <v>4901.160902217987</v>
+        <v>3091.744093660315</v>
       </c>
       <c r="J4" t="n">
         <v>1079589.365674657</v>
@@ -610,25 +610,25 @@
         <v>51502</v>
       </c>
       <c r="C5" t="n">
-        <v>6691.691461437282</v>
+        <v>3197.3759637148</v>
       </c>
       <c r="D5" t="n">
         <v>1079589.365674657</v>
       </c>
       <c r="E5" t="n">
-        <v>6630.004831519404</v>
+        <v>3127.026777572429</v>
       </c>
       <c r="F5" t="n">
         <v>1079589.365674657</v>
       </c>
       <c r="G5" t="n">
-        <v>5677.190789609691</v>
+        <v>3121.58187018792</v>
       </c>
       <c r="H5" t="n">
         <v>1079589.365674657</v>
       </c>
       <c r="I5" t="n">
-        <v>5806.508883222008</v>
+        <v>3219.307029484622</v>
       </c>
       <c r="J5" t="n">
         <v>1079589.365674657</v>
@@ -647,25 +647,25 @@
         <v>53328</v>
       </c>
       <c r="C6" t="n">
-        <v>6700.862192115643</v>
+        <v>3197.3759637148</v>
       </c>
       <c r="D6" t="n">
         <v>1079589.365674657</v>
       </c>
       <c r="E6" t="n">
-        <v>6640.948281087326</v>
+        <v>3127.026777572429</v>
       </c>
       <c r="F6" t="n">
         <v>1079589.365674657</v>
       </c>
       <c r="G6" t="n">
-        <v>5677.588645936792</v>
+        <v>3121.58187018792</v>
       </c>
       <c r="H6" t="n">
         <v>1079589.365674657</v>
       </c>
       <c r="I6" t="n">
-        <v>5806.906739549109</v>
+        <v>3219.307029484622</v>
       </c>
       <c r="J6" t="n">
         <v>1079589.365674657</v>
@@ -677,7 +677,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh</t>
+          <t>BLVL_Li-ion_s_12.5 kWh</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -687,34 +687,34 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1619.384048511985</v>
+        <v>1555.001614803371</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1619.384048511985</v>
+        <v>898.7675280900396</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>901.4621675577108</v>
+        <v>898.7675280900396</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>901.4621675577108</v>
+        <v>1555.001614803371</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh</t>
+          <t>BLVL_Li-ion_s_12.5 kWh</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -724,34 +724,34 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1619.384048511985</v>
+        <v>1555.001614803371</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1619.384048511985</v>
+        <v>1135.173222815758</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1160.090642460342</v>
+        <v>1135.173222815758</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1160.090642460342</v>
+        <v>1555.001614803371</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh</t>
+          <t>BLVL_Li-ion_s_12.5 kWh</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -761,34 +761,34 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1619.384048511985</v>
+        <v>1555.001614803371</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1619.384048511985</v>
+        <v>1244.806277927109</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1280.029503811638</v>
+        <v>1244.806277927109</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1280.029503811638</v>
+        <v>1555.001614803371</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh</t>
+          <t>BLVL_Li-ion_s_12.5 kWh</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -798,34 +798,34 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1619.384048511985</v>
+        <v>1555.001614803371</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1619.384048511985</v>
+        <v>1306.663170741263</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1347.701113284926</v>
+        <v>1306.663170741263</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1347.701113284926</v>
+        <v>1555.001614803371</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh</t>
+          <t>BLVL_Li-ion_s_12.5 kWh</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -835,28 +835,28 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1619.384048511985</v>
+        <v>1555.001614803371</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1619.384048511985</v>
+        <v>1346.080567749224</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1390.823853135284</v>
+        <v>1346.080567749224</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1390.823853135284</v>
+        <v>1555.001614803371</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="12">
@@ -878,7 +878,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>27.34287872281026</v>
+        <v>7.347147807951172</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -890,7 +890,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>7.347147807951172</v>
+        <v>27.34287872281026</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -915,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>27.34287872281026</v>
+        <v>11.07072285027803</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -927,7 +927,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>11.07072285027803</v>
+        <v>27.34287872281026</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -952,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>27.34287872281026</v>
+        <v>13.27059094294789</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -964,7 +964,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>13.27059094294789</v>
+        <v>27.34287872281026</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>27.34287872281026</v>
+        <v>14.70723143869926</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>14.70723143869926</v>
+        <v>27.34287872281026</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1026,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>27.34287872281026</v>
+        <v>15.71417382440975</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>15.71417382440975</v>
+        <v>27.34287872281026</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1054,28 +1054,28 @@
         <v>46023</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6894127497199123</v>
+        <v>0.8571510216557604</v>
       </c>
       <c r="D17" t="n">
         <v>27.34287872281026</v>
       </c>
       <c r="E17" t="n">
-        <v>0.690103491160321</v>
+        <v>0.8571138744706368</v>
       </c>
       <c r="F17" t="n">
-        <v>27.34287872281026</v>
+        <v>7.347147807951172</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6901103598569772</v>
+        <v>0.857126870388901</v>
       </c>
       <c r="H17" t="n">
         <v>7.347147807951172</v>
       </c>
       <c r="I17" t="n">
-        <v>0.689414668960596</v>
+        <v>0.8571357876099975</v>
       </c>
       <c r="J17" t="n">
-        <v>7.347147807951172</v>
+        <v>27.34287872281026</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
@@ -1091,28 +1091,28 @@
         <v>47849</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6972113351050577</v>
+        <v>0.9814206021971674</v>
       </c>
       <c r="D18" t="n">
         <v>27.34287872281026</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6976239895808937</v>
+        <v>1.008130542818419</v>
       </c>
       <c r="F18" t="n">
-        <v>27.34287872281026</v>
+        <v>11.07072285027803</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6976296789968723</v>
+        <v>0.9922593767585118</v>
       </c>
       <c r="H18" t="n">
         <v>11.07072285027803</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6976938351840734</v>
+        <v>0.991795142067611</v>
       </c>
       <c r="J18" t="n">
-        <v>11.07072285027803</v>
+        <v>27.34287872281026</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
@@ -1128,28 +1128,28 @@
         <v>49675</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7038791567282776</v>
+        <v>1.120672034435365</v>
       </c>
       <c r="D19" t="n">
         <v>27.34287872281026</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7038850274433082</v>
+        <v>1.118687793798841</v>
       </c>
       <c r="F19" t="n">
-        <v>27.34287872281026</v>
+        <v>13.27059094294789</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7040907131480567</v>
+        <v>1.118235219331155</v>
       </c>
       <c r="H19" t="n">
         <v>13.27059094294789</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7041730005167468</v>
+        <v>1.123194485875984</v>
       </c>
       <c r="J19" t="n">
-        <v>13.27059094294789</v>
+        <v>27.34287872281026</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
@@ -1165,28 +1165,28 @@
         <v>51502</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7104866790486678</v>
+        <v>1.192422371478665</v>
       </c>
       <c r="D20" t="n">
         <v>27.34287872281026</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7105922735820145</v>
+        <v>1.190108694766611</v>
       </c>
       <c r="F20" t="n">
-        <v>27.34287872281026</v>
+        <v>14.70723143869926</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7106044808274045</v>
+        <v>1.18329495261209</v>
       </c>
       <c r="H20" t="n">
         <v>14.70723143869926</v>
       </c>
       <c r="I20" t="n">
-        <v>0.710599052345294</v>
+        <v>1.194875799143992</v>
       </c>
       <c r="J20" t="n">
-        <v>14.70723143869926</v>
+        <v>27.34287872281026</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
@@ -1202,28 +1202,28 @@
         <v>53328</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7034489197629951</v>
+        <v>1.189973919512179</v>
       </c>
       <c r="D21" t="n">
         <v>27.34287872281026</v>
       </c>
       <c r="E21" t="n">
-        <v>0.70350126863647</v>
+        <v>1.180942064866327</v>
       </c>
       <c r="F21" t="n">
-        <v>27.34287872281026</v>
+        <v>15.71417382440975</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7039572958796189</v>
+        <v>1.18083767264949</v>
       </c>
       <c r="H21" t="n">
         <v>15.71417382440975</v>
       </c>
       <c r="I21" t="n">
-        <v>0.703442943385683</v>
+        <v>1.194753017340081</v>
       </c>
       <c r="J21" t="n">
-        <v>15.71417382440975</v>
+        <v>27.34287872281026</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
@@ -1239,25 +1239,25 @@
         <v>46023</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2450490608376471</v>
+        <v>0.1992693981509584</v>
       </c>
       <c r="D22" t="n">
         <v>11</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2478453145389155</v>
+        <v>0.1991925395659942</v>
       </c>
       <c r="F22" t="n">
         <v>11</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2478683538118557</v>
+        <v>0.1991884920497604</v>
       </c>
       <c r="H22" t="n">
         <v>11</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2450568302916767</v>
+        <v>0.199270352022934</v>
       </c>
       <c r="J22" t="n">
         <v>11</v>
@@ -1276,25 +1276,25 @@
         <v>47849</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2503271913635294</v>
+        <v>0.2174077686655556</v>
       </c>
       <c r="D23" t="n">
         <v>11</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2543512085964706</v>
+        <v>0.22105662694</v>
       </c>
       <c r="F23" t="n">
         <v>11</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2544066891723171</v>
+        <v>0.2203484560482353</v>
       </c>
       <c r="H23" t="n">
         <v>11</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2543589780505002</v>
+        <v>0.2195623259856873</v>
       </c>
       <c r="J23" t="n">
         <v>11</v>
@@ -1313,25 +1313,25 @@
         <v>49675</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2615935284292178</v>
+        <v>0.2321342784965494</v>
       </c>
       <c r="D24" t="n">
         <v>11</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2630453505729412</v>
+        <v>0.2324505628182226</v>
       </c>
       <c r="F24" t="n">
         <v>11</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2651580300641753</v>
+        <v>0.2324492149667718</v>
       </c>
       <c r="H24" t="n">
         <v>11</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2659014844957994</v>
+        <v>0.2322495834249111</v>
       </c>
       <c r="J24" t="n">
         <v>11</v>
@@ -1350,25 +1350,25 @@
         <v>51502</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2846471836692178</v>
+        <v>0.2441128931522036</v>
       </c>
       <c r="D25" t="n">
         <v>11</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2851270991070589</v>
+        <v>0.2448036121134201</v>
       </c>
       <c r="F25" t="n">
         <v>11</v>
       </c>
       <c r="G25" t="n">
-        <v>0.287282827530254</v>
+        <v>0.2448036121134201</v>
       </c>
       <c r="H25" t="n">
         <v>11</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2853710322606761</v>
+        <v>0.244603578685269</v>
       </c>
       <c r="J25" t="n">
         <v>11</v>
@@ -1387,25 +1387,25 @@
         <v>53328</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2846471836692178</v>
+        <v>0.2450049389506973</v>
       </c>
       <c r="D26" t="n">
         <v>11</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2851270991070589</v>
+        <v>0.2460823801840084</v>
       </c>
       <c r="F26" t="n">
         <v>11</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2881310591449957</v>
+        <v>0.2460823801840084</v>
       </c>
       <c r="H26" t="n">
         <v>11</v>
       </c>
       <c r="I26" t="n">
-        <v>0.285418401343117</v>
+        <v>0.2458823467558572</v>
       </c>
       <c r="J26" t="n">
         <v>11</v>
@@ -1602,7 +1602,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DLVL_H2_Tank_s_100 MWh</t>
+          <t>DLVL_H2_Tank_s_16.7 MWh</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0.0488804107201733</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1630,16 +1630,16 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0488804107201733</v>
+        <v>10</v>
       </c>
       <c r="K32" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DLVL_H2_Tank_s_100 MWh</t>
+          <t>DLVL_H2_Tank_s_16.7 MWh</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
@@ -1649,13 +1649,13 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0.08192846775049219</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1667,16 +1667,16 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.08192846775049219</v>
+        <v>10</v>
       </c>
       <c r="K33" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DLVL_H2_Tank_s_100 MWh</t>
+          <t>DLVL_H2_Tank_s_16.7 MWh</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1686,13 +1686,13 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>0.1064719951694473</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1704,16 +1704,16 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0.1064719951694473</v>
+        <v>10</v>
       </c>
       <c r="K34" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DLVL_H2_Tank_s_100 MWh</t>
+          <t>DLVL_H2_Tank_s_16.7 MWh</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
@@ -1723,13 +1723,13 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>0.1257660092222253</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1741,16 +1741,16 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0.1257660092222253</v>
+        <v>10</v>
       </c>
       <c r="K35" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DLVL_H2_Tank_s_100 MWh</t>
+          <t>DLVL_H2_Tank_s_16.7 MWh</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1760,13 +1760,13 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>0.1415431203502453</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0.1415431203502453</v>
+        <v>10</v>
       </c>
       <c r="K36" t="n">
-        <v>100</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="37">
@@ -1794,25 +1794,25 @@
         <v>46023</v>
       </c>
       <c r="C37" t="n">
-        <v>0.02898744244259066</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
         <v>18.5072462687084</v>
       </c>
       <c r="E37" t="n">
-        <v>0.02901901919415249</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>18.5072462687084</v>
       </c>
       <c r="G37" t="n">
-        <v>0.02901933319171392</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>18.5072462687084</v>
       </c>
       <c r="I37" t="n">
-        <v>0.02898753017930792</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>18.5072462687084</v>
@@ -1831,25 +1831,25 @@
         <v>47849</v>
       </c>
       <c r="C38" t="n">
-        <v>0.02934394920305474</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>18.5072462687084</v>
       </c>
       <c r="E38" t="n">
-        <v>0.02936281340766439</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>18.5072462687084</v>
       </c>
       <c r="G38" t="n">
-        <v>0.02936307349525198</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>18.5072462687084</v>
       </c>
       <c r="I38" t="n">
-        <v>0.02936600634952403</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>18.5072462687084</v>
@@ -1868,25 +1868,25 @@
         <v>49675</v>
       </c>
       <c r="C39" t="n">
-        <v>0.02964876390583051</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
         <v>18.5072462687084</v>
       </c>
       <c r="E39" t="n">
-        <v>0.02965459421564152</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>18.5072462687084</v>
       </c>
       <c r="G39" t="n">
-        <v>0.02969927294668604</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>18.5072462687084</v>
       </c>
       <c r="I39" t="n">
-        <v>0.02967871928314523</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>18.5072462687084</v>
@@ -1905,25 +1905,25 @@
         <v>51502</v>
       </c>
       <c r="C40" t="n">
-        <v>0.03258282236788212</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
         <v>18.5072462687084</v>
       </c>
       <c r="E40" t="n">
-        <v>0.03268769014643565</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
         <v>18.5072462687084</v>
       </c>
       <c r="G40" t="n">
-        <v>0.03317987002623384</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>18.5072462687084</v>
       </c>
       <c r="I40" t="n">
-        <v>0.03274313640951252</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
         <v>18.5072462687084</v>
@@ -1942,25 +1942,25 @@
         <v>53328</v>
       </c>
       <c r="C41" t="n">
-        <v>0.03290454850665572</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>18.5072462687084</v>
       </c>
       <c r="E41" t="n">
-        <v>0.03301185037251767</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>18.5072462687084</v>
       </c>
       <c r="G41" t="n">
-        <v>0.03367762285007358</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>18.5072462687084</v>
       </c>
       <c r="I41" t="n">
-        <v>0.03308110003793839</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>18.5072462687084</v>
@@ -1972,7 +1972,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DLVL_Li-ion_s_8 MWh</t>
+          <t>DLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -1982,34 +1982,34 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>2.376290242402129</v>
+        <v>6.336773979739009</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>2.376290242402129</v>
+        <v>0.09225645693266066</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.03459617134974775</v>
+        <v>0.09225645693266066</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.03459617134974775</v>
+        <v>6.336773979739009</v>
       </c>
       <c r="K42" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DLVL_Li-ion_s_8 MWh</t>
+          <t>DLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
@@ -2019,145 +2019,145 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>2.376290242402129</v>
+        <v>6.336773979739009</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>2.376290242402129</v>
+        <v>0.1627797101487544</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.06104239130578291</v>
+        <v>0.1627797101487544</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0.06104239130578291</v>
+        <v>6.336773979739009</v>
       </c>
       <c r="K43" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DLVL_Li-ion_s_8 MWh</t>
+          <t>DLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>2.376290242402129</v>
+        <v>6.336773979739009</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>2.376290242402129</v>
+        <v>0.2211165551130434</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.08291870816739128</v>
+        <v>0.2211165551130434</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>0.08291870816739128</v>
+        <v>6.336773979739009</v>
       </c>
       <c r="K44" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DLVL_Li-ion_s_8 MWh</t>
+          <t>DLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>2.376290242402129</v>
+        <v>6.336773979739009</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>2.376290242402129</v>
+        <v>0.2713026233531382</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1017384837574268</v>
+        <v>0.2713026233531382</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J45" t="n">
-        <v>0.1017384837574268</v>
+        <v>6.336773979739009</v>
       </c>
       <c r="K45" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DLVL_Li-ion_s_8 MWh</t>
+          <t>DLVL_Li-ion_s_3 MWh</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D46" t="n">
-        <v>2.376290242402129</v>
+        <v>6.336773979739009</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>2.376290242402129</v>
+        <v>0.3155451959087551</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1183294484657832</v>
+        <v>0.3155451959087551</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J46" t="n">
-        <v>0.1183294484657832</v>
+        <v>6.336773979739009</v>
       </c>
       <c r="K46" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DLVL_NMC_s_4.15 MWh</t>
+          <t>DLVL_NaNiCl_s_4.15 MWh</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
@@ -2167,25 +2167,25 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>4.580800467281213</v>
+        <v>4.580800467281212</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>4.580800467281213</v>
+        <v>0.06669141465011615</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.06669141465011616</v>
+        <v>0.06669141465011615</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0.06669141465011616</v>
+        <v>4.580800467281212</v>
       </c>
       <c r="K47" t="n">
         <v>4.15</v>
@@ -2194,7 +2194,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DLVL_NMC_s_4.15 MWh</t>
+          <t>DLVL_NaNiCl_s_4.15 MWh</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2204,13 +2204,13 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>4.580800467281213</v>
+        <v>4.580800467281212</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>4.580800467281213</v>
+        <v>0.1176720796256056</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0.1176720796256056</v>
+        <v>4.580800467281212</v>
       </c>
       <c r="K48" t="n">
         <v>4.15</v>
@@ -2231,7 +2231,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DLVL_NMC_s_4.15 MWh</t>
+          <t>DLVL_NaNiCl_s_4.15 MWh</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
@@ -2241,13 +2241,13 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>4.580800467281213</v>
+        <v>4.580800467281212</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>4.580800467281213</v>
+        <v>0.1598432928528025</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -2259,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0.1598432928528025</v>
+        <v>4.580800467281212</v>
       </c>
       <c r="K49" t="n">
         <v>4.15</v>
@@ -2268,7 +2268,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DLVL_NMC_s_4.15 MWh</t>
+          <t>DLVL_NaNiCl_s_4.15 MWh</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -2278,13 +2278,13 @@
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>4.580800467281213</v>
+        <v>4.580800467281212</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>4.580800467281213</v>
+        <v>0.1961223783275698</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0.1961223783275698</v>
+        <v>4.580800467281212</v>
       </c>
       <c r="K50" t="n">
         <v>4.15</v>
@@ -2305,7 +2305,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DLVL_NMC_s_4.15 MWh</t>
+          <t>DLVL_NaNiCl_s_4.15 MWh</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
@@ -2315,13 +2315,13 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>4.580800467281213</v>
+        <v>4.580800467281212</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>4.580800467281213</v>
+        <v>0.2281049608978953</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -2333,7 +2333,7 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0.2281049608978953</v>
+        <v>4.580800467281212</v>
       </c>
       <c r="K51" t="n">
         <v>4.15</v>
@@ -2358,19 +2358,19 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
+        <v>0.0009225645693266068</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.0009225645693266068</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
         <v>0.0633677397973901</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.0009225645693266069</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0.0009225645693266069</v>
       </c>
       <c r="K52" t="n">
         <v>300</v>
@@ -2395,7 +2395,7 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0633677397973901</v>
+        <v>0.001627797101487544</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0.001627797101487544</v>
+        <v>0.0633677397973901</v>
       </c>
       <c r="K53" t="n">
         <v>300</v>
@@ -2432,7 +2432,7 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0633677397973901</v>
+        <v>0.002211165551130434</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -2444,7 +2444,7 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0.002211165551130434</v>
+        <v>0.0633677397973901</v>
       </c>
       <c r="K54" t="n">
         <v>300</v>
@@ -2469,19 +2469,19 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
+        <v>0.002713026233531382</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.002713026233531382</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
         <v>0.0633677397973901</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.002713026233531383</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0.002713026233531383</v>
       </c>
       <c r="K55" t="n">
         <v>300</v>
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0.0633677397973901</v>
+        <v>0.003155451959087552</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2518,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0.003155451959087552</v>
+        <v>0.0633677397973901</v>
       </c>
       <c r="K56" t="n">
         <v>300</v>
@@ -2527,7 +2527,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+          <t>DLVL_VRF_s_500 kWh</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
@@ -2537,34 +2537,34 @@
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>100</v>
+        <v>38.02064387843406</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>100</v>
+        <v>0.5535387415959639</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>100</v>
+        <v>0.5535387415959639</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>100</v>
+        <v>38.02064387843406</v>
       </c>
       <c r="K57" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+          <t>DLVL_VRF_s_500 kWh</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -2574,34 +2574,34 @@
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>100</v>
+        <v>38.02064387843406</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>100</v>
+        <v>0.9766782608925265</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>100</v>
+        <v>0.9766782608925265</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>100</v>
+        <v>38.02064387843406</v>
       </c>
       <c r="K58" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+          <t>DLVL_VRF_s_500 kWh</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
@@ -2611,34 +2611,34 @@
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>100</v>
+        <v>38.02064387843406</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>100</v>
+        <v>1.32669933067826</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>100</v>
+        <v>1.32669933067826</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>100</v>
+        <v>38.02064387843406</v>
       </c>
       <c r="K59" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+          <t>DLVL_VRF_s_500 kWh</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -2648,34 +2648,34 @@
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>100</v>
+        <v>38.02064387843406</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>100</v>
+        <v>1.627815740118829</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>100</v>
+        <v>1.627815740118829</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>100</v>
+        <v>38.02064387843406</v>
       </c>
       <c r="K60" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
+          <t>DLVL_VRF_s_500 kWh</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
@@ -2685,34 +2685,34 @@
         <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>100</v>
+        <v>38.02064387843406</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>100</v>
+        <v>1.893271175452531</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>100</v>
+        <v>1.893271175452531</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>100</v>
+        <v>38.02064387843406</v>
       </c>
       <c r="K61" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -2743,13 +2743,13 @@
         <v>100</v>
       </c>
       <c r="K62" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
@@ -2780,13 +2780,13 @@
         <v>100</v>
       </c>
       <c r="K63" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -2817,13 +2817,13 @@
         <v>100</v>
       </c>
       <c r="K64" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
@@ -2854,13 +2854,13 @@
         <v>100</v>
       </c>
       <c r="K65" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
+          <t>H2_Alcaline_Electrolyzer_s_2 MW</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -2891,568 +2891,568 @@
         <v>100</v>
       </c>
       <c r="K66" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_40 kW</t>
+          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C67" t="n">
-        <v>0.1349121862912588</v>
+        <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>16.241803305</v>
+        <v>100</v>
       </c>
       <c r="E67" t="n">
-        <v>0.1349121862912588</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>16.241803305</v>
+        <v>100</v>
       </c>
       <c r="G67" t="n">
-        <v>0.1172224124973282</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>16.241803305</v>
+        <v>100</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1289917227637565</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>16.241803305</v>
+        <v>100</v>
       </c>
       <c r="K67" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_40 kW</t>
+          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C68" t="n">
-        <v>0.180249231161595</v>
+        <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>16.241803305</v>
+        <v>100</v>
       </c>
       <c r="E68" t="n">
-        <v>0.180249231161595</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>16.241803305</v>
+        <v>100</v>
       </c>
       <c r="G68" t="n">
-        <v>0.1660839022481308</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>16.241803305</v>
+        <v>100</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1751542721247414</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>16.241803305</v>
+        <v>100</v>
       </c>
       <c r="K68" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_40 kW</t>
+          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C69" t="n">
-        <v>2.091117652661598</v>
+        <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>16.241803305</v>
+        <v>100</v>
       </c>
       <c r="E69" t="n">
-        <v>2.091117652661598</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>16.241803305</v>
+        <v>100</v>
       </c>
       <c r="G69" t="n">
-        <v>1.872540267901668</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>16.241803305</v>
+        <v>100</v>
       </c>
       <c r="I69" t="n">
-        <v>1.788478927848562</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>16.241803305</v>
+        <v>100</v>
       </c>
       <c r="K69" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_40 kW</t>
+          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C70" t="n">
-        <v>2.846610131471202</v>
+        <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>16.241803305</v>
+        <v>100</v>
       </c>
       <c r="E70" t="n">
-        <v>2.846610131471202</v>
+        <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>16.241803305</v>
+        <v>100</v>
       </c>
       <c r="G70" t="n">
-        <v>2.623458797690411</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>16.241803305</v>
+        <v>100</v>
       </c>
       <c r="I70" t="n">
-        <v>2.82396566114002</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>16.241803305</v>
+        <v>100</v>
       </c>
       <c r="K70" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_40 kW</t>
+          <t>H2_PEM_Electrolyzer_s_0.1 MW</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C71" t="n">
-        <v>2.801273086600866</v>
+        <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>16.241803305</v>
+        <v>100</v>
       </c>
       <c r="E71" t="n">
-        <v>2.801273086600866</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>16.241803305</v>
+        <v>100</v>
       </c>
       <c r="G71" t="n">
-        <v>2.574597307939609</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>16.241803305</v>
+        <v>100</v>
       </c>
       <c r="I71" t="n">
-        <v>2.777803111779035</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>16.241803305</v>
+        <v>100</v>
       </c>
       <c r="K71" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_8 kW</t>
+          <t>HW_ElectricBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C72" t="n">
-        <v>0.1375288603743197</v>
+        <v>0.4666346213363456</v>
       </c>
       <c r="D72" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="E72" t="n">
-        <v>0.1375288603743197</v>
+        <v>0.4399348962387115</v>
       </c>
       <c r="F72" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="G72" t="n">
-        <v>0.1255113484494612</v>
+        <v>0.4423760198147426</v>
       </c>
       <c r="H72" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1156081728219056</v>
+        <v>0.4559322039742895</v>
       </c>
       <c r="J72" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="K72" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_8 kW</t>
+          <t>HW_ElectricBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C73" t="n">
-        <v>0.1387055908309011</v>
+        <v>0.4666346213363456</v>
       </c>
       <c r="D73" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="E73" t="n">
-        <v>0.138705590830901</v>
+        <v>0.4399348962387115</v>
       </c>
       <c r="F73" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="G73" t="n">
-        <v>0.1255113484494612</v>
+        <v>0.4423760198147426</v>
       </c>
       <c r="H73" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1156081728219056</v>
+        <v>0.4559322039742895</v>
       </c>
       <c r="J73" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="K73" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_8 kW</t>
+          <t>HW_ElectricBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C74" t="n">
-        <v>1.143431408551582</v>
+        <v>4.215244052254378</v>
       </c>
       <c r="D74" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="E74" t="n">
-        <v>1.143431408551582</v>
+        <v>4.205585560082188</v>
       </c>
       <c r="F74" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="G74" t="n">
-        <v>1.087368095653426</v>
+        <v>4.318337056412603</v>
       </c>
       <c r="H74" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="I74" t="n">
-        <v>1.087368095653426</v>
+        <v>4.035397247413817</v>
       </c>
       <c r="J74" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="K74" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_8 kW</t>
+          <t>HW_ElectricBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C75" t="n">
-        <v>8.956776194948699</v>
+        <v>5.066020855341987</v>
       </c>
       <c r="D75" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="E75" t="n">
-        <v>8.956776194948699</v>
+        <v>5.099671517764358</v>
       </c>
       <c r="F75" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="G75" t="n">
-        <v>8.956776194948699</v>
+        <v>5.12336342873078</v>
       </c>
       <c r="H75" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="I75" t="n">
-        <v>8.956776194948699</v>
+        <v>5.021665378562341</v>
       </c>
       <c r="J75" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="K75" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>HW_ElectricBoiler_s_8 kW</t>
+          <t>HW_ElectricBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C76" t="n">
-        <v>8.955599464492117</v>
+        <v>5.066020855341987</v>
       </c>
       <c r="D76" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="E76" t="n">
-        <v>8.955599464492117</v>
+        <v>5.099671517764358</v>
       </c>
       <c r="F76" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="G76" t="n">
-        <v>8.956776194948699</v>
+        <v>5.12336342873078</v>
       </c>
       <c r="H76" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="I76" t="n">
-        <v>8.956776194948699</v>
+        <v>5.021665378562341</v>
       </c>
       <c r="J76" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="K76" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_40 kW</t>
+          <t>HW_ElectricBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>4.04168289</v>
       </c>
       <c r="D77" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>3.549588528011054</v>
       </c>
       <c r="F77" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>3.788591244833378</v>
       </c>
       <c r="H77" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>4.049826127189359</v>
       </c>
       <c r="J77" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="K77" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_40 kW</t>
+          <t>HW_ElectricBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>4.04168289</v>
       </c>
       <c r="D78" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>3.549588528011054</v>
       </c>
       <c r="F78" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>3.788591244833378</v>
       </c>
       <c r="H78" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>4.049826127189359</v>
       </c>
       <c r="J78" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="K78" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_40 kW</t>
+          <t>HW_ElectricBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>16.26173969014897</v>
       </c>
       <c r="D79" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>15.00244100125849</v>
       </c>
       <c r="F79" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>15.23960911846148</v>
       </c>
       <c r="H79" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>16.27235153247842</v>
       </c>
       <c r="J79" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="K79" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_40 kW</t>
+          <t>HW_ElectricBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>23.34003694618821</v>
       </c>
       <c r="D80" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>21.94754313720228</v>
       </c>
       <c r="F80" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>21.93857424881679</v>
       </c>
       <c r="H80" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>23.33484408677814</v>
       </c>
       <c r="J80" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="K80" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_40 kW</t>
+          <t>HW_ElectricBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>23.34003694618821</v>
       </c>
       <c r="D81" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>21.94754313720228</v>
       </c>
       <c r="F81" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>21.93857424881679</v>
       </c>
       <c r="H81" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>23.33484408677814</v>
       </c>
       <c r="J81" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="K81" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_8 kW</t>
+          <t>HW_GasBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -3462,34 +3462,34 @@
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="K82" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_8 kW</t>
+          <t>HW_GasBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
@@ -3499,34 +3499,34 @@
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="K83" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_8 kW</t>
+          <t>HW_GasBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -3536,34 +3536,34 @@
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="K84" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_8 kW</t>
+          <t>HW_GasBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
@@ -3573,34 +3573,34 @@
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="K85" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>HW_GasBoiler_s_8 kW</t>
+          <t>HW_GasBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -3610,34 +3610,34 @@
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="K86" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_40 kW</t>
+          <t>HW_GasBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
@@ -3647,34 +3647,34 @@
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="K87" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_40 kW</t>
+          <t>HW_GasBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -3684,34 +3684,34 @@
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="K88" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_40 kW</t>
+          <t>HW_GasBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
@@ -3721,34 +3721,34 @@
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="K89" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_40 kW</t>
+          <t>HW_GasBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -3758,34 +3758,34 @@
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="K90" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_40 kW</t>
+          <t>HW_GasBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
@@ -3795,219 +3795,219 @@
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="K91" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_8 kW</t>
+          <t>HW_HPAS_s_40 kW</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>0.03330175583566848</v>
       </c>
       <c r="D92" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>0.04966336888525662</v>
       </c>
       <c r="F92" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>0.04958328834458596</v>
       </c>
       <c r="H92" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>0.03320040693826391</v>
       </c>
       <c r="J92" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="K92" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_8 kW</t>
+          <t>HW_HPAS_s_40 kW</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>0.03330175583566848</v>
       </c>
       <c r="D93" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>0.04966336888525662</v>
       </c>
       <c r="F93" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>0.04958328834458596</v>
       </c>
       <c r="H93" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>0.03320040693826391</v>
       </c>
       <c r="J93" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="K93" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_8 kW</t>
+          <t>HW_HPAS_s_40 kW</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>0.9032949246235034</v>
       </c>
       <c r="D94" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>1.014506676885257</v>
       </c>
       <c r="F94" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>1.014426596344586</v>
       </c>
       <c r="H94" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>0.9010614552584367</v>
       </c>
       <c r="J94" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="K94" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_8 kW</t>
+          <t>HW_HPAS_s_40 kW</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>0.8944829538012633</v>
       </c>
       <c r="D95" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>1.013336583326865</v>
       </c>
       <c r="F95" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>1.013761140257561</v>
       </c>
       <c r="H95" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>0.8915382444981981</v>
       </c>
       <c r="J95" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="K95" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>HW_HPAS_s_8 kW</t>
+          <t>HW_HPAS_s_40 kW</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>0.8944829538012632</v>
       </c>
       <c r="D96" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>1.013336583326865</v>
       </c>
       <c r="F96" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>1.013761140257561</v>
       </c>
       <c r="H96" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>0.8915382444981981</v>
       </c>
       <c r="J96" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="K96" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_40 kW</t>
+          <t>HW_HPAS_s_8 kW</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
@@ -4017,34 +4017,34 @@
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>0.02860839000000002</v>
       </c>
       <c r="F97" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>0.02723731920879604</v>
       </c>
       <c r="H97" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="K97" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_40 kW</t>
+          <t>HW_HPAS_s_8 kW</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -4054,145 +4054,145 @@
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>0.02860839000000002</v>
       </c>
       <c r="F98" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>0.02723731920879604</v>
       </c>
       <c r="H98" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="K98" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_40 kW</t>
+          <t>HW_HPAS_s_8 kW</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>0.08809559096784873</v>
       </c>
       <c r="D99" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>0.1915236908200446</v>
       </c>
       <c r="F99" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>0.191987219648211</v>
       </c>
       <c r="H99" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>0.08562698582769117</v>
       </c>
       <c r="J99" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="K99" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_40 kW</t>
+          <t>HW_HPAS_s_8 kW</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>1.55197422258693</v>
       </c>
       <c r="D100" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="E100" t="n">
-        <v>0</v>
+        <v>2.662567003818474</v>
       </c>
       <c r="F100" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>2.671535892203872</v>
       </c>
       <c r="H100" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>1.557167081996984</v>
       </c>
       <c r="J100" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="K100" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_40 kW</t>
+          <t>HW_HPAS_s_8 kW</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>1.55197422258693</v>
       </c>
       <c r="D101" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>2.662567003818474</v>
       </c>
       <c r="F101" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>2.671535892203872</v>
       </c>
       <c r="H101" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>1.557167081996984</v>
       </c>
       <c r="J101" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="K101" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_8 kW</t>
+          <t>HW_HPGS_s_40 kW</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
@@ -4202,34 +4202,34 @@
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="E102" t="n">
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="K102" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_8 kW</t>
+          <t>HW_HPGS_s_40 kW</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
@@ -4239,34 +4239,34 @@
         <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="I103" t="n">
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="K103" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_8 kW</t>
+          <t>HW_HPGS_s_40 kW</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
@@ -4276,34 +4276,34 @@
         <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="E104" t="n">
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="I104" t="n">
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="K104" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_8 kW</t>
+          <t>HW_HPGS_s_40 kW</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
@@ -4313,34 +4313,34 @@
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="E105" t="n">
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="K105" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>HW_HPGS_s_8 kW</t>
+          <t>HW_HPGS_s_40 kW</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
@@ -4350,34 +4350,34 @@
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="I106" t="n">
         <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="K106" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_40 kW</t>
+          <t>HW_HPGS_s_8 kW</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
@@ -4387,34 +4387,34 @@
         <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="E107" t="n">
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="I107" t="n">
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="K107" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_40 kW</t>
+          <t>HW_HPGS_s_8 kW</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
@@ -4424,34 +4424,34 @@
         <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="E108" t="n">
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="I108" t="n">
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="K108" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_40 kW</t>
+          <t>HW_HPGS_s_8 kW</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
@@ -4461,34 +4461,34 @@
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="E109" t="n">
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="I109" t="n">
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="K109" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_40 kW</t>
+          <t>HW_HPGS_s_8 kW</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
@@ -4498,34 +4498,34 @@
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="E110" t="n">
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="I110" t="n">
         <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="K110" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_40 kW</t>
+          <t>HW_HPGS_s_8 kW</t>
         </is>
       </c>
       <c r="B111" s="2" t="n">
@@ -4535,34 +4535,34 @@
         <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="E111" t="n">
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>16.241803305</v>
+        <v>116.256416724</v>
       </c>
       <c r="K111" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_8 kW</t>
+          <t>HW_OilBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
@@ -4572,34 +4572,34 @@
         <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="E112" t="n">
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="I112" t="n">
         <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="K112" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_8 kW</t>
+          <t>HW_OilBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
@@ -4609,34 +4609,34 @@
         <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="E113" t="n">
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="I113" t="n">
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="K113" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_8 kW</t>
+          <t>HW_OilBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
@@ -4646,34 +4646,34 @@
         <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="E114" t="n">
         <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="I114" t="n">
         <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="K114" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_8 kW</t>
+          <t>HW_OilBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
@@ -4683,34 +4683,34 @@
         <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="E115" t="n">
         <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="K115" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>HW_OilBoiler_s_8 kW</t>
+          <t>HW_OilBoiler_s_40 kW</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
@@ -4720,34 +4720,34 @@
         <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="E116" t="n">
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="I116" t="n">
         <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>116.256416724</v>
+        <v>16.241803305</v>
       </c>
       <c r="K116" t="n">
-        <v>0.008</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>RE_GPV_s_1 MW</t>
+          <t>HW_OilBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
@@ -4757,182 +4757,182 @@
         <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>86.12029024877936</v>
+        <v>116.256416724</v>
       </c>
       <c r="E117" t="n">
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>86.12029024877936</v>
+        <v>116.256416724</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>0</v>
+        <v>116.256416724</v>
       </c>
       <c r="I117" t="n">
         <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>0</v>
+        <v>116.256416724</v>
       </c>
       <c r="K117" t="n">
-        <v>1</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>RE_GPV_s_1 MW</t>
+          <t>HW_OilBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C118" t="n">
-        <v>30.91744076928672</v>
+        <v>0</v>
       </c>
       <c r="D118" t="n">
-        <v>86.12029024877936</v>
+        <v>116.256416724</v>
       </c>
       <c r="E118" t="n">
-        <v>30.81185235055051</v>
+        <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>86.12029024877936</v>
+        <v>116.256416724</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>0</v>
+        <v>116.256416724</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>0</v>
+        <v>116.256416724</v>
       </c>
       <c r="K118" t="n">
-        <v>1</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>RE_GPV_s_1 MW</t>
+          <t>HW_OilBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B119" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C119" t="n">
-        <v>37.82131609047958</v>
+        <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>86.12029024877936</v>
+        <v>116.256416724</v>
       </c>
       <c r="E119" t="n">
-        <v>37.45194786984256</v>
+        <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>86.12029024877936</v>
+        <v>116.256416724</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>116.256416724</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
+        <v>116.256416724</v>
       </c>
       <c r="K119" t="n">
-        <v>1</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>RE_GPV_s_1 MW</t>
+          <t>HW_OilBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C120" t="n">
-        <v>47.91830740981699</v>
+        <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>86.12029024877936</v>
+        <v>116.256416724</v>
       </c>
       <c r="E120" t="n">
-        <v>47.89435890192804</v>
+        <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>86.12029024877936</v>
+        <v>116.256416724</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>116.256416724</v>
       </c>
       <c r="I120" t="n">
         <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>0</v>
+        <v>116.256416724</v>
       </c>
       <c r="K120" t="n">
-        <v>1</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>RE_GPV_s_1 MW</t>
+          <t>HW_OilBoiler_s_8 kW</t>
         </is>
       </c>
       <c r="B121" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C121" t="n">
-        <v>47.91830740981699</v>
+        <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>86.12029024877936</v>
+        <v>116.256416724</v>
       </c>
       <c r="E121" t="n">
-        <v>47.89435890192804</v>
+        <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>86.12029024877936</v>
+        <v>116.256416724</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>0</v>
+        <v>116.256416724</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>0</v>
+        <v>116.256416724</v>
       </c>
       <c r="K121" t="n">
-        <v>1</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_10 kW</t>
+          <t>RE_GPV_s_1 MW</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
@@ -4942,182 +4942,182 @@
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>1049.59381421211</v>
+        <v>86.12029024877936</v>
       </c>
       <c r="E122" t="n">
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>1049.59381421211</v>
+        <v>0</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>487.6972421926781</v>
+        <v>0</v>
       </c>
       <c r="I122" t="n">
         <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>487.6972421926781</v>
+        <v>86.12029024877936</v>
       </c>
       <c r="K122" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_10 kW</t>
+          <t>RE_GPV_s_1 MW</t>
         </is>
       </c>
       <c r="B123" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C123" t="n">
-        <v>0</v>
+        <v>30.30314539839646</v>
       </c>
       <c r="D123" t="n">
-        <v>1049.59381421211</v>
+        <v>86.12029024877936</v>
       </c>
       <c r="E123" t="n">
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>1049.59381421211</v>
+        <v>0</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>653.1311678369761</v>
+        <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
+        <v>30.20431097340229</v>
       </c>
       <c r="J123" t="n">
-        <v>653.1311678369761</v>
+        <v>86.12029024877936</v>
       </c>
       <c r="K123" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_10 kW</t>
+          <t>RE_GPV_s_1 MW</t>
         </is>
       </c>
       <c r="B124" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C124" t="n">
-        <v>0</v>
+        <v>39.70516753315746</v>
       </c>
       <c r="D124" t="n">
-        <v>1049.59381421211</v>
+        <v>86.12029024877936</v>
       </c>
       <c r="E124" t="n">
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>1049.59381421211</v>
+        <v>0</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>738.7033098821516</v>
+        <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>37.73287256743881</v>
       </c>
       <c r="J124" t="n">
-        <v>738.7033098821516</v>
+        <v>86.12029024877936</v>
       </c>
       <c r="K124" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_10 kW</t>
+          <t>RE_GPV_s_1 MW</t>
         </is>
       </c>
       <c r="B125" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C125" t="n">
-        <v>0</v>
+        <v>53.16158962423919</v>
       </c>
       <c r="D125" t="n">
-        <v>1049.59381421211</v>
+        <v>86.12029024877936</v>
       </c>
       <c r="E125" t="n">
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>1049.59381421211</v>
+        <v>0</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>790.3401491694015</v>
+        <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>0</v>
+        <v>53.16113393812113</v>
       </c>
       <c r="J125" t="n">
-        <v>790.3401491694015</v>
+        <v>86.12029024877936</v>
       </c>
       <c r="K125" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_10 kW</t>
+          <t>RE_GPV_s_1 MW</t>
         </is>
       </c>
       <c r="B126" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C126" t="n">
-        <v>0</v>
+        <v>54.95102273430234</v>
       </c>
       <c r="D126" t="n">
-        <v>1049.59381421211</v>
+        <v>86.12029024877936</v>
       </c>
       <c r="E126" t="n">
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>1049.59381421211</v>
+        <v>0</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>824.7800038886719</v>
+        <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>54.74138455067398</v>
       </c>
       <c r="J126" t="n">
-        <v>824.7800038886719</v>
+        <v>86.12029024877936</v>
       </c>
       <c r="K126" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_30 kW</t>
+          <t>RE_RTPV_s_10 kW</t>
         </is>
       </c>
       <c r="B127" s="2" t="n">
@@ -5127,34 +5127,34 @@
         <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>85.87539526263001</v>
+        <v>1049.59381421211</v>
       </c>
       <c r="E127" t="n">
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>85.87539526263001</v>
+        <v>487.6972421926781</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>45.44216573983687</v>
+        <v>487.6972421926781</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>45.44216573983687</v>
+        <v>1049.59381421211</v>
       </c>
       <c r="K127" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_30 kW</t>
+          <t>RE_RTPV_s_10 kW</t>
         </is>
       </c>
       <c r="B128" s="2" t="n">
@@ -5164,34 +5164,34 @@
         <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>85.87539526263001</v>
+        <v>1049.59381421211</v>
       </c>
       <c r="E128" t="n">
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>85.87539526263001</v>
+        <v>653.1311678369761</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>57.34654141949712</v>
+        <v>653.1311678369761</v>
       </c>
       <c r="I128" t="n">
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>57.34654141949712</v>
+        <v>1049.59381421211</v>
       </c>
       <c r="K128" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_30 kW</t>
+          <t>RE_RTPV_s_10 kW</t>
         </is>
       </c>
       <c r="B129" s="2" t="n">
@@ -5201,34 +5201,34 @@
         <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>85.87539526263001</v>
+        <v>1049.59381421211</v>
       </c>
       <c r="E129" t="n">
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>85.87539526263001</v>
+        <v>738.7033098821516</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>63.50418364827012</v>
+        <v>738.7033098821516</v>
       </c>
       <c r="I129" t="n">
         <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>63.50418364827012</v>
+        <v>1049.59381421211</v>
       </c>
       <c r="K129" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_30 kW</t>
+          <t>RE_RTPV_s_10 kW</t>
         </is>
       </c>
       <c r="B130" s="2" t="n">
@@ -5238,34 +5238,34 @@
         <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>85.87539526263001</v>
+        <v>1049.59381421211</v>
       </c>
       <c r="E130" t="n">
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>85.87539526263001</v>
+        <v>790.3401491694015</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>67.21989269278222</v>
+        <v>790.3401491694015</v>
       </c>
       <c r="I130" t="n">
         <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>67.21989269278222</v>
+        <v>1049.59381421211</v>
       </c>
       <c r="K130" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>RE_RTPV_s_30 kW</t>
+          <t>RE_RTPV_s_10 kW</t>
         </is>
       </c>
       <c r="B131" s="2" t="n">
@@ -5275,34 +5275,34 @@
         <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>85.87539526263001</v>
+        <v>1049.59381421211</v>
       </c>
       <c r="E131" t="n">
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>85.87539526263001</v>
+        <v>824.7800038886719</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>69.69813267490433</v>
+        <v>824.7800038886719</v>
       </c>
       <c r="I131" t="n">
         <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>69.69813267490433</v>
+        <v>1049.59381421211</v>
       </c>
       <c r="K131" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>RE_WT_s_3.3 MW</t>
+          <t>RE_RTPV_s_30 kW</t>
         </is>
       </c>
       <c r="B132" s="2" t="n">
@@ -5312,34 +5312,34 @@
         <v>0</v>
       </c>
       <c r="D132" t="n">
-        <v>0.6060606060606061</v>
+        <v>85.87539526263001</v>
       </c>
       <c r="E132" t="n">
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>0.6060606060606061</v>
+        <v>45.44216573983687</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>0</v>
+        <v>45.44216573983687</v>
       </c>
       <c r="I132" t="n">
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>0</v>
+        <v>85.87539526263001</v>
       </c>
       <c r="K132" t="n">
-        <v>3.3</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>RE_WT_s_3.3 MW</t>
+          <t>RE_RTPV_s_30 kW</t>
         </is>
       </c>
       <c r="B133" s="2" t="n">
@@ -5349,34 +5349,34 @@
         <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>0.6060606060606061</v>
+        <v>85.87539526263001</v>
       </c>
       <c r="E133" t="n">
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>0.6060606060606061</v>
+        <v>57.34654141949712</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>0</v>
+        <v>57.34654141949712</v>
       </c>
       <c r="I133" t="n">
         <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>0</v>
+        <v>85.87539526263001</v>
       </c>
       <c r="K133" t="n">
-        <v>3.3</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>RE_WT_s_3.3 MW</t>
+          <t>RE_RTPV_s_30 kW</t>
         </is>
       </c>
       <c r="B134" s="2" t="n">
@@ -5386,34 +5386,34 @@
         <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>0.6060606060606061</v>
+        <v>85.87539526263001</v>
       </c>
       <c r="E134" t="n">
         <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>0.6060606060606061</v>
+        <v>63.50418364827012</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>0</v>
+        <v>63.50418364827012</v>
       </c>
       <c r="I134" t="n">
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>0</v>
+        <v>85.87539526263001</v>
       </c>
       <c r="K134" t="n">
-        <v>3.3</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>RE_WT_s_3.3 MW</t>
+          <t>RE_RTPV_s_30 kW</t>
         </is>
       </c>
       <c r="B135" s="2" t="n">
@@ -5423,34 +5423,34 @@
         <v>0</v>
       </c>
       <c r="D135" t="n">
-        <v>0.6060606060606061</v>
+        <v>85.87539526263001</v>
       </c>
       <c r="E135" t="n">
         <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>0.6060606060606061</v>
+        <v>67.21989269278222</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>0</v>
+        <v>67.21989269278222</v>
       </c>
       <c r="I135" t="n">
         <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>0</v>
+        <v>85.87539526263001</v>
       </c>
       <c r="K135" t="n">
-        <v>3.3</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>RE_WT_s_3.3 MW</t>
+          <t>RE_RTPV_s_30 kW</t>
         </is>
       </c>
       <c r="B136" s="2" t="n">
@@ -5460,34 +5460,34 @@
         <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>0.6060606060606061</v>
+        <v>85.87539526263001</v>
       </c>
       <c r="E136" t="n">
         <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>0.6060606060606061</v>
+        <v>69.69813267490433</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>0</v>
+        <v>69.69813267490433</v>
       </c>
       <c r="I136" t="n">
         <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>0</v>
+        <v>85.87539526263001</v>
       </c>
       <c r="K136" t="n">
-        <v>3.3</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_17 kW</t>
+          <t>RE_WT_s_3.3 MW</t>
         </is>
       </c>
       <c r="B137" s="2" t="n">
@@ -5497,34 +5497,34 @@
         <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>1114.849449025352</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="E137" t="n">
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>1114.849449025352</v>
+        <v>0</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>1114.849449025352</v>
+        <v>0</v>
       </c>
       <c r="I137" t="n">
         <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>1114.849449025352</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="K137" t="n">
-        <v>0.017</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_17 kW</t>
+          <t>RE_WT_s_3.3 MW</t>
         </is>
       </c>
       <c r="B138" s="2" t="n">
@@ -5534,34 +5534,34 @@
         <v>0</v>
       </c>
       <c r="D138" t="n">
-        <v>1114.849449025352</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="E138" t="n">
         <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>1114.849449025352</v>
+        <v>0</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>1114.849449025352</v>
+        <v>0</v>
       </c>
       <c r="I138" t="n">
         <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>1114.849449025352</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="K138" t="n">
-        <v>0.017</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_17 kW</t>
+          <t>RE_WT_s_3.3 MW</t>
         </is>
       </c>
       <c r="B139" s="2" t="n">
@@ -5571,34 +5571,34 @@
         <v>0</v>
       </c>
       <c r="D139" t="n">
-        <v>1114.849449025352</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="E139" t="n">
         <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>1114.849449025352</v>
+        <v>0</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>1114.849449025352</v>
+        <v>0</v>
       </c>
       <c r="I139" t="n">
         <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>1114.849449025352</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="K139" t="n">
-        <v>0.017</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_17 kW</t>
+          <t>RE_WT_s_3.3 MW</t>
         </is>
       </c>
       <c r="B140" s="2" t="n">
@@ -5608,34 +5608,34 @@
         <v>0</v>
       </c>
       <c r="D140" t="n">
-        <v>1114.849449025352</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="E140" t="n">
         <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>1114.849449025352</v>
+        <v>0</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>1114.849449025352</v>
+        <v>0</v>
       </c>
       <c r="I140" t="n">
         <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>1114.849449025352</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="K140" t="n">
-        <v>0.017</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_17 kW</t>
+          <t>RE_WT_s_3.3 MW</t>
         </is>
       </c>
       <c r="B141" s="2" t="n">
@@ -5645,34 +5645,34 @@
         <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>1114.849449025352</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="E141" t="n">
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>1114.849449025352</v>
+        <v>0</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>1114.849449025352</v>
+        <v>0</v>
       </c>
       <c r="I141" t="n">
         <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>1114.849449025352</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="K141" t="n">
-        <v>0.017</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_80 kW</t>
+          <t>SH_GasBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B142" s="2" t="n">
@@ -5682,34 +5682,34 @@
         <v>0</v>
       </c>
       <c r="D142" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E142" t="n">
         <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
       </c>
       <c r="H142" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="I142" t="n">
         <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K142" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_80 kW</t>
+          <t>SH_GasBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B143" s="2" t="n">
@@ -5719,34 +5719,34 @@
         <v>0</v>
       </c>
       <c r="D143" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E143" t="n">
         <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
       </c>
       <c r="H143" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="I143" t="n">
         <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K143" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_80 kW</t>
+          <t>SH_GasBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B144" s="2" t="n">
@@ -5756,34 +5756,34 @@
         <v>0</v>
       </c>
       <c r="D144" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E144" t="n">
         <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
       </c>
       <c r="H144" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="I144" t="n">
         <v>0</v>
       </c>
       <c r="J144" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K144" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_80 kW</t>
+          <t>SH_GasBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B145" s="2" t="n">
@@ -5793,34 +5793,34 @@
         <v>0</v>
       </c>
       <c r="D145" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E145" t="n">
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
       </c>
       <c r="H145" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="I145" t="n">
         <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K145" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SH_GasBoiler_s_80 kW</t>
+          <t>SH_GasBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B146" s="2" t="n">
@@ -5830,589 +5830,589 @@
         <v>0</v>
       </c>
       <c r="D146" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E146" t="n">
         <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
       </c>
       <c r="H146" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="I146" t="n">
         <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K146" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_17 kW</t>
+          <t>SH_GasBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B147" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C147" t="n">
-        <v>5.377631610602566</v>
+        <v>0</v>
       </c>
       <c r="D147" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E147" t="n">
         <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>352.6532537643785</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="I147" t="n">
-        <v>1.339016391190267</v>
+        <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>352.6532537643785</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="K147" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_17 kW</t>
+          <t>SH_GasBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B148" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C148" t="n">
-        <v>136.2893000850349</v>
+        <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E148" t="n">
-        <v>128.2806464516402</v>
+        <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="G148" t="n">
-        <v>126.7175277378064</v>
+        <v>0</v>
       </c>
       <c r="H148" t="n">
-        <v>490.4252151544125</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="I148" t="n">
-        <v>132.7095589261965</v>
+        <v>0</v>
       </c>
       <c r="J148" t="n">
-        <v>490.4252151544125</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="K148" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_17 kW</t>
+          <t>SH_GasBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B149" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C149" t="n">
-        <v>315.9352434870914</v>
+        <v>0</v>
       </c>
       <c r="D149" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E149" t="n">
-        <v>308.0801613111206</v>
+        <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="G149" t="n">
-        <v>307.2373900384558</v>
+        <v>0</v>
       </c>
       <c r="H149" t="n">
-        <v>565.3337341205297</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="I149" t="n">
-        <v>312.2032910723375</v>
+        <v>0</v>
       </c>
       <c r="J149" t="n">
-        <v>565.3337341205297</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="K149" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_17 kW</t>
+          <t>SH_GasBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B150" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C150" t="n">
-        <v>354.5444844478889</v>
+        <v>0</v>
       </c>
       <c r="D150" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E150" t="n">
-        <v>345.7436026499595</v>
+        <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="G150" t="n">
-        <v>343.3987589836762</v>
+        <v>0</v>
       </c>
       <c r="H150" t="n">
-        <v>611.4456499978917</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="I150" t="n">
-        <v>353.9430437628016</v>
+        <v>0</v>
       </c>
       <c r="J150" t="n">
-        <v>611.4456499978917</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="K150" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_17 kW</t>
+          <t>SH_GasBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B151" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C151" t="n">
-        <v>349.4649747159745</v>
+        <v>0</v>
       </c>
       <c r="D151" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E151" t="n">
-        <v>332.4686437718734</v>
+        <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="G151" t="n">
-        <v>332.3939015760608</v>
+        <v>0</v>
       </c>
       <c r="H151" t="n">
-        <v>642.411379623893</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="I151" t="n">
-        <v>347.8055132234666</v>
+        <v>0</v>
       </c>
       <c r="J151" t="n">
-        <v>642.411379623893</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="K151" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_80 kW</t>
+          <t>SH_HPAS_s_17 kW</t>
         </is>
       </c>
       <c r="B152" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C152" t="n">
-        <v>1.674413698263089</v>
+        <v>0.2559649031497945</v>
       </c>
       <c r="D152" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E152" t="n">
-        <v>1.419776609468461</v>
+        <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>88.66010124321591</v>
+        <v>352.6532537643785</v>
       </c>
       <c r="G152" t="n">
-        <v>1.42810697984234</v>
+        <v>0.2298100401001068</v>
       </c>
       <c r="H152" t="n">
-        <v>32.08317947568147</v>
+        <v>352.6532537643785</v>
       </c>
       <c r="I152" t="n">
-        <v>1.657413501499705</v>
+        <v>0</v>
       </c>
       <c r="J152" t="n">
-        <v>32.08317947568147</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K152" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_80 kW</t>
+          <t>SH_HPAS_s_17 kW</t>
         </is>
       </c>
       <c r="B153" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C153" t="n">
-        <v>6.035281241305491</v>
+        <v>152.3945266602952</v>
       </c>
       <c r="D153" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E153" t="n">
-        <v>5.266580000444137</v>
+        <v>133.5656852153181</v>
       </c>
       <c r="F153" t="n">
-        <v>88.66010124321591</v>
+        <v>490.4252151544125</v>
       </c>
       <c r="G153" t="n">
-        <v>5.220740133703622</v>
+        <v>153.1638842203302</v>
       </c>
       <c r="H153" t="n">
-        <v>42.30982916219012</v>
+        <v>490.4252151544125</v>
       </c>
       <c r="I153" t="n">
-        <v>5.831740506360457</v>
+        <v>135.0761690959137</v>
       </c>
       <c r="J153" t="n">
-        <v>42.30982916219012</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K153" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_80 kW</t>
+          <t>SH_HPAS_s_17 kW</t>
         </is>
       </c>
       <c r="B154" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C154" t="n">
-        <v>26.94723290375057</v>
+        <v>324.5389465331958</v>
       </c>
       <c r="D154" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E154" t="n">
-        <v>26.19675316725324</v>
+        <v>321.4883072209868</v>
       </c>
       <c r="F154" t="n">
-        <v>88.66010124321591</v>
+        <v>565.3337341205297</v>
       </c>
       <c r="G154" t="n">
-        <v>26.29685572469824</v>
+        <v>324.383599343885</v>
       </c>
       <c r="H154" t="n">
-        <v>47.8701998956294</v>
+        <v>565.3337341205297</v>
       </c>
       <c r="I154" t="n">
-        <v>26.93129334457766</v>
+        <v>321.9473817720294</v>
       </c>
       <c r="J154" t="n">
-        <v>47.8701998956294</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K154" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_80 kW</t>
+          <t>SH_HPAS_s_17 kW</t>
         </is>
       </c>
       <c r="B155" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C155" t="n">
-        <v>27.71709949671776</v>
+        <v>352.5718144996843</v>
       </c>
       <c r="D155" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E155" t="n">
-        <v>27.1779890023094</v>
+        <v>352.1744486283392</v>
       </c>
       <c r="F155" t="n">
-        <v>88.66010124321591</v>
+        <v>611.4456499978917</v>
       </c>
       <c r="G155" t="n">
-        <v>27.19845488137893</v>
+        <v>352.5887270852014</v>
       </c>
       <c r="H155" t="n">
-        <v>51.29303285303004</v>
+        <v>611.4456499978917</v>
       </c>
       <c r="I155" t="n">
-        <v>27.70374400850626</v>
+        <v>352.1370917082411</v>
       </c>
       <c r="J155" t="n">
-        <v>51.29303285303004</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K155" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SH_HPAS_s_80 kW</t>
+          <t>SH_HPAS_s_17 kW</t>
         </is>
       </c>
       <c r="B156" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C156" t="n">
-        <v>27.38980213580767</v>
+        <v>352.4064691953316</v>
       </c>
       <c r="D156" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E156" t="n">
-        <v>26.89660058105128</v>
+        <v>334.0014347144311</v>
       </c>
       <c r="F156" t="n">
-        <v>88.66010124321591</v>
+        <v>642.411379623893</v>
       </c>
       <c r="G156" t="n">
-        <v>26.90232477054856</v>
+        <v>352.4338623738886</v>
       </c>
       <c r="H156" t="n">
-        <v>53.59158232548581</v>
+        <v>642.411379623893</v>
       </c>
       <c r="I156" t="n">
-        <v>27.27575245407262</v>
+        <v>334.2281391909278</v>
       </c>
       <c r="J156" t="n">
-        <v>53.59158232548581</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K156" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_17 kW</t>
+          <t>SH_HPAS_s_80 kW</t>
         </is>
       </c>
       <c r="B157" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C157" t="n">
-        <v>0</v>
+        <v>1.647960634776094</v>
       </c>
       <c r="D157" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E157" t="n">
-        <v>0</v>
+        <v>1.47410888166861</v>
       </c>
       <c r="F157" t="n">
-        <v>1114.849449025352</v>
+        <v>32.08317947568147</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>1.607996973000245</v>
       </c>
       <c r="H157" t="n">
-        <v>352.6532537643785</v>
+        <v>32.08317947568147</v>
       </c>
       <c r="I157" t="n">
-        <v>0</v>
+        <v>1.495603679798146</v>
       </c>
       <c r="J157" t="n">
-        <v>352.6532537643785</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="K157" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_17 kW</t>
+          <t>SH_HPAS_s_80 kW</t>
         </is>
       </c>
       <c r="B158" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C158" t="n">
-        <v>0</v>
+        <v>5.509026041070794</v>
       </c>
       <c r="D158" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E158" t="n">
-        <v>0</v>
+        <v>5.216422776449562</v>
       </c>
       <c r="F158" t="n">
-        <v>1114.849449025352</v>
+        <v>42.30982916219012</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>5.546689959068223</v>
       </c>
       <c r="H158" t="n">
-        <v>490.4252151544125</v>
+        <v>42.30982916219012</v>
       </c>
       <c r="I158" t="n">
-        <v>0</v>
+        <v>5.301123667182241</v>
       </c>
       <c r="J158" t="n">
-        <v>490.4252151544125</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="K158" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_17 kW</t>
+          <t>SH_HPAS_s_80 kW</t>
         </is>
       </c>
       <c r="B159" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C159" t="n">
-        <v>0</v>
+        <v>25.67576794225949</v>
       </c>
       <c r="D159" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E159" t="n">
-        <v>0</v>
+        <v>24.41226481256559</v>
       </c>
       <c r="F159" t="n">
-        <v>1114.849449025352</v>
+        <v>47.8701998956294</v>
       </c>
       <c r="G159" t="n">
-        <v>0</v>
+        <v>25.67978872619167</v>
       </c>
       <c r="H159" t="n">
-        <v>565.3337341205297</v>
+        <v>47.8701998956294</v>
       </c>
       <c r="I159" t="n">
-        <v>0</v>
+        <v>24.25243683634492</v>
       </c>
       <c r="J159" t="n">
-        <v>565.3337341205297</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="K159" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_17 kW</t>
+          <t>SH_HPAS_s_80 kW</t>
         </is>
       </c>
       <c r="B160" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C160" t="n">
-        <v>0</v>
+        <v>27.16702777438002</v>
       </c>
       <c r="D160" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E160" t="n">
-        <v>0</v>
+        <v>26.68485835395162</v>
       </c>
       <c r="F160" t="n">
-        <v>1114.849449025352</v>
+        <v>51.29303285303004</v>
       </c>
       <c r="G160" t="n">
-        <v>0</v>
+        <v>27.31761514530233</v>
       </c>
       <c r="H160" t="n">
-        <v>611.4456499978917</v>
+        <v>51.29303285303004</v>
       </c>
       <c r="I160" t="n">
-        <v>0</v>
+        <v>26.78719019916214</v>
       </c>
       <c r="J160" t="n">
-        <v>611.4456499978917</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="K160" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_17 kW</t>
+          <t>SH_HPAS_s_80 kW</t>
         </is>
       </c>
       <c r="B161" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C161" t="n">
-        <v>0</v>
+        <v>26.61079774236698</v>
       </c>
       <c r="D161" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E161" t="n">
-        <v>0</v>
+        <v>26.65413383340034</v>
       </c>
       <c r="F161" t="n">
-        <v>1114.849449025352</v>
+        <v>53.59158232548581</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>26.74265528087519</v>
       </c>
       <c r="H161" t="n">
-        <v>642.411379623893</v>
+        <v>53.59158232548581</v>
       </c>
       <c r="I161" t="n">
-        <v>0</v>
+        <v>26.51202941300698</v>
       </c>
       <c r="J161" t="n">
-        <v>642.411379623893</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="K161" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_80 kW</t>
+          <t>SH_HPGS_s_17 kW</t>
         </is>
       </c>
       <c r="B162" s="2" t="n">
@@ -6422,34 +6422,34 @@
         <v>0</v>
       </c>
       <c r="D162" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E162" t="n">
         <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>88.66010124321591</v>
+        <v>352.6532537643785</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>32.08317947568147</v>
+        <v>352.6532537643785</v>
       </c>
       <c r="I162" t="n">
         <v>0</v>
       </c>
       <c r="J162" t="n">
-        <v>32.08317947568147</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K162" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_80 kW</t>
+          <t>SH_HPGS_s_17 kW</t>
         </is>
       </c>
       <c r="B163" s="2" t="n">
@@ -6459,34 +6459,34 @@
         <v>0</v>
       </c>
       <c r="D163" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E163" t="n">
         <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>88.66010124321591</v>
+        <v>490.4252151544125</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>42.30982916219012</v>
+        <v>490.4252151544125</v>
       </c>
       <c r="I163" t="n">
         <v>0</v>
       </c>
       <c r="J163" t="n">
-        <v>42.30982916219012</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K163" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_80 kW</t>
+          <t>SH_HPGS_s_17 kW</t>
         </is>
       </c>
       <c r="B164" s="2" t="n">
@@ -6496,34 +6496,34 @@
         <v>0</v>
       </c>
       <c r="D164" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E164" t="n">
         <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>88.66010124321591</v>
+        <v>565.3337341205297</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
       </c>
       <c r="H164" t="n">
-        <v>47.8701998956294</v>
+        <v>565.3337341205297</v>
       </c>
       <c r="I164" t="n">
         <v>0</v>
       </c>
       <c r="J164" t="n">
-        <v>47.8701998956294</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K164" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_80 kW</t>
+          <t>SH_HPGS_s_17 kW</t>
         </is>
       </c>
       <c r="B165" s="2" t="n">
@@ -6533,34 +6533,34 @@
         <v>0</v>
       </c>
       <c r="D165" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E165" t="n">
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>88.66010124321591</v>
+        <v>611.4456499978917</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
       </c>
       <c r="H165" t="n">
-        <v>51.29303285303004</v>
+        <v>611.4456499978917</v>
       </c>
       <c r="I165" t="n">
         <v>0</v>
       </c>
       <c r="J165" t="n">
-        <v>51.29303285303004</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K165" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SH_HPGS_s_80 kW</t>
+          <t>SH_HPGS_s_17 kW</t>
         </is>
       </c>
       <c r="B166" s="2" t="n">
@@ -6570,34 +6570,34 @@
         <v>0</v>
       </c>
       <c r="D166" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E166" t="n">
         <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>88.66010124321591</v>
+        <v>642.411379623893</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
       </c>
       <c r="H166" t="n">
-        <v>53.59158232548581</v>
+        <v>642.411379623893</v>
       </c>
       <c r="I166" t="n">
         <v>0</v>
       </c>
       <c r="J166" t="n">
-        <v>53.59158232548581</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K166" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_17 kW</t>
+          <t>SH_HPGS_s_80 kW</t>
         </is>
       </c>
       <c r="B167" s="2" t="n">
@@ -6607,34 +6607,34 @@
         <v>0</v>
       </c>
       <c r="D167" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E167" t="n">
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>1114.849449025352</v>
+        <v>32.08317947568147</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>1114.849449025352</v>
+        <v>32.08317947568147</v>
       </c>
       <c r="I167" t="n">
         <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="K167" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_17 kW</t>
+          <t>SH_HPGS_s_80 kW</t>
         </is>
       </c>
       <c r="B168" s="2" t="n">
@@ -6644,145 +6644,145 @@
         <v>0</v>
       </c>
       <c r="D168" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E168" t="n">
         <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>1114.849449025352</v>
+        <v>42.30982916219012</v>
       </c>
       <c r="G168" t="n">
-        <v>1.032044408251227</v>
+        <v>0</v>
       </c>
       <c r="H168" t="n">
-        <v>1114.849449025352</v>
+        <v>42.30982916219012</v>
       </c>
       <c r="I168" t="n">
         <v>0</v>
       </c>
       <c r="J168" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="K168" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_17 kW</t>
+          <t>SH_HPGS_s_80 kW</t>
         </is>
       </c>
       <c r="B169" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C169" t="n">
-        <v>104.5041870878486</v>
+        <v>0</v>
       </c>
       <c r="D169" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E169" t="n">
-        <v>105.4833337980041</v>
+        <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>1114.849449025352</v>
+        <v>47.8701998956294</v>
       </c>
       <c r="G169" t="n">
-        <v>117.5058363120643</v>
+        <v>0</v>
       </c>
       <c r="H169" t="n">
-        <v>1114.849449025352</v>
+        <v>47.8701998956294</v>
       </c>
       <c r="I169" t="n">
-        <v>109.5392831444812</v>
+        <v>0</v>
       </c>
       <c r="J169" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="K169" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_17 kW</t>
+          <t>SH_HPGS_s_80 kW</t>
         </is>
       </c>
       <c r="B170" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C170" t="n">
-        <v>111.1714089638304</v>
+        <v>0</v>
       </c>
       <c r="D170" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E170" t="n">
-        <v>121.3616399564218</v>
+        <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>1114.849449025352</v>
+        <v>51.29303285303004</v>
       </c>
       <c r="G170" t="n">
-        <v>145.6893291346514</v>
+        <v>0</v>
       </c>
       <c r="H170" t="n">
-        <v>1114.849449025352</v>
+        <v>51.29303285303004</v>
       </c>
       <c r="I170" t="n">
-        <v>131.7841036606337</v>
+        <v>0</v>
       </c>
       <c r="J170" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="K170" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_17 kW</t>
+          <t>SH_HPGS_s_80 kW</t>
         </is>
       </c>
       <c r="B171" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C171" t="n">
-        <v>129.1077653833088</v>
+        <v>0</v>
       </c>
       <c r="D171" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E171" t="n">
-        <v>147.4543414289199</v>
+        <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>1114.849449025352</v>
+        <v>53.59158232548581</v>
       </c>
       <c r="G171" t="n">
-        <v>169.7445525169911</v>
+        <v>0</v>
       </c>
       <c r="H171" t="n">
-        <v>1114.849449025352</v>
+        <v>53.59158232548581</v>
       </c>
       <c r="I171" t="n">
-        <v>150.9720001746929</v>
+        <v>0</v>
       </c>
       <c r="J171" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="K171" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_80 kW</t>
+          <t>SH_HydrogenBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B172" s="2" t="n">
@@ -6792,182 +6792,182 @@
         <v>0</v>
       </c>
       <c r="D172" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E172" t="n">
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
       </c>
       <c r="H172" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="I172" t="n">
         <v>0</v>
       </c>
       <c r="J172" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K172" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_80 kW</t>
+          <t>SH_HydrogenBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B173" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C173" t="n">
-        <v>0.1523761928824859</v>
+        <v>0</v>
       </c>
       <c r="D173" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E173" t="n">
-        <v>0.1632294015727809</v>
+        <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="G173" t="n">
-        <v>0.1553453603369206</v>
+        <v>0</v>
       </c>
       <c r="H173" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1422802667665692</v>
+        <v>0</v>
       </c>
       <c r="J173" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K173" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_80 kW</t>
+          <t>SH_HydrogenBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B174" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C174" t="n">
-        <v>1.878293464514055</v>
+        <v>46.5202983140767</v>
       </c>
       <c r="D174" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E174" t="n">
-        <v>2.53149391125547</v>
+        <v>49.52846699103554</v>
       </c>
       <c r="F174" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="G174" t="n">
-        <v>2.186487570902002</v>
+        <v>46.55886676187098</v>
       </c>
       <c r="H174" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="I174" t="n">
-        <v>1.542640212504902</v>
+        <v>48.98618882120361</v>
       </c>
       <c r="J174" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K174" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_80 kW</t>
+          <t>SH_HydrogenBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B175" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C175" t="n">
-        <v>11.48674944917886</v>
+        <v>80.10751380295119</v>
       </c>
       <c r="D175" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E175" t="n">
-        <v>12.01977931746161</v>
+        <v>80.62693085949316</v>
       </c>
       <c r="F175" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="G175" t="n">
-        <v>11.79427458855525</v>
+        <v>80.16500546262355</v>
       </c>
       <c r="H175" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="I175" t="n">
-        <v>11.39700679528479</v>
+        <v>80.52678552812091</v>
       </c>
       <c r="J175" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K175" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SH_HydrogenBoiler_s_80 kW</t>
+          <t>SH_HydrogenBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B176" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C176" t="n">
-        <v>12.72254792391485</v>
+        <v>102.6065151156153</v>
       </c>
       <c r="D176" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E176" t="n">
-        <v>13.20966885254563</v>
+        <v>121.0698181241821</v>
       </c>
       <c r="F176" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="G176" t="n">
-        <v>13.0461264135529</v>
+        <v>102.6187696853185</v>
       </c>
       <c r="H176" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="I176" t="n">
-        <v>12.78934403267441</v>
+        <v>120.7899983308322</v>
       </c>
       <c r="J176" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K176" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_17 kW</t>
+          <t>SH_HydrogenBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B177" s="2" t="n">
@@ -6977,182 +6977,182 @@
         <v>0</v>
       </c>
       <c r="D177" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E177" t="n">
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
       </c>
       <c r="H177" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="I177" t="n">
         <v>0</v>
       </c>
       <c r="J177" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="K177" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_17 kW</t>
+          <t>SH_HydrogenBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B178" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C178" t="n">
-        <v>0</v>
+        <v>0.07299008439058666</v>
       </c>
       <c r="D178" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E178" t="n">
-        <v>0</v>
+        <v>0.08089390170519327</v>
       </c>
       <c r="F178" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="G178" t="n">
-        <v>0</v>
+        <v>0.07417556912841897</v>
       </c>
       <c r="H178" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="I178" t="n">
-        <v>0</v>
+        <v>0.0804832334835677</v>
       </c>
       <c r="J178" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="K178" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_17 kW</t>
+          <t>SH_HydrogenBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B179" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C179" t="n">
-        <v>0</v>
+        <v>2.135531982843997</v>
       </c>
       <c r="D179" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E179" t="n">
-        <v>0</v>
+        <v>3.3395508631579</v>
       </c>
       <c r="F179" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="G179" t="n">
-        <v>0</v>
+        <v>1.942108483295013</v>
       </c>
       <c r="H179" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="I179" t="n">
-        <v>0</v>
+        <v>3.240801683267161</v>
       </c>
       <c r="J179" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="K179" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_17 kW</t>
+          <t>SH_HydrogenBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B180" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="C180" t="n">
-        <v>0</v>
+        <v>6.348955181876266</v>
       </c>
       <c r="D180" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E180" t="n">
-        <v>0</v>
+        <v>7.165649700547412</v>
       </c>
       <c r="F180" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="G180" t="n">
-        <v>0</v>
+        <v>6.590276840356596</v>
       </c>
       <c r="H180" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="I180" t="n">
-        <v>0</v>
+        <v>6.614444429679935</v>
       </c>
       <c r="J180" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="K180" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_17 kW</t>
+          <t>SH_HydrogenBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B181" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="C181" t="n">
-        <v>0</v>
+        <v>8.116209898830817</v>
       </c>
       <c r="D181" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E181" t="n">
-        <v>0</v>
+        <v>8.209330635463449</v>
       </c>
       <c r="F181" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="G181" t="n">
-        <v>0</v>
+        <v>8.135834122398222</v>
       </c>
       <c r="H181" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="I181" t="n">
-        <v>0</v>
+        <v>8.152284356385895</v>
       </c>
       <c r="J181" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="K181" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_80 kW</t>
+          <t>SH_OilBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B182" s="2" t="n">
@@ -7162,34 +7162,34 @@
         <v>0</v>
       </c>
       <c r="D182" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E182" t="n">
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
       </c>
       <c r="H182" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="I182" t="n">
         <v>0</v>
       </c>
       <c r="J182" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K182" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_80 kW</t>
+          <t>SH_OilBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B183" s="2" t="n">
@@ -7199,34 +7199,34 @@
         <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E183" t="n">
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
       </c>
       <c r="H183" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="I183" t="n">
         <v>0</v>
       </c>
       <c r="J183" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K183" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_80 kW</t>
+          <t>SH_OilBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B184" s="2" t="n">
@@ -7236,34 +7236,34 @@
         <v>0</v>
       </c>
       <c r="D184" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E184" t="n">
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
       </c>
       <c r="H184" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="I184" t="n">
         <v>0</v>
       </c>
       <c r="J184" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K184" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_80 kW</t>
+          <t>SH_OilBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B185" s="2" t="n">
@@ -7273,34 +7273,34 @@
         <v>0</v>
       </c>
       <c r="D185" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E185" t="n">
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
       </c>
       <c r="H185" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="I185" t="n">
         <v>0</v>
       </c>
       <c r="J185" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K185" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SH_OilBoiler_s_80 kW</t>
+          <t>SH_OilBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B186" s="2" t="n">
@@ -7310,34 +7310,34 @@
         <v>0</v>
       </c>
       <c r="D186" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E186" t="n">
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
       </c>
       <c r="H186" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="I186" t="n">
         <v>0</v>
       </c>
       <c r="J186" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K186" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_17 kW</t>
+          <t>SH_OilBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B187" s="2" t="n">
@@ -7347,34 +7347,34 @@
         <v>0</v>
       </c>
       <c r="D187" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E187" t="n">
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
       </c>
       <c r="H187" t="n">
-        <v>67.28827832216861</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="I187" t="n">
         <v>0</v>
       </c>
       <c r="J187" t="n">
-        <v>67.28827832216861</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="K187" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_17 kW</t>
+          <t>SH_OilBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B188" s="2" t="n">
@@ -7384,34 +7384,34 @@
         <v>0</v>
       </c>
       <c r="D188" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E188" t="n">
         <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
       </c>
       <c r="H188" t="n">
-        <v>84.67898534372102</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="I188" t="n">
         <v>0</v>
       </c>
       <c r="J188" t="n">
-        <v>84.67898534372102</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="K188" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_17 kW</t>
+          <t>SH_OilBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B189" s="2" t="n">
@@ -7421,34 +7421,34 @@
         <v>0</v>
       </c>
       <c r="D189" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E189" t="n">
         <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
       </c>
       <c r="H189" t="n">
-        <v>99.07527913276064</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="I189" t="n">
         <v>0</v>
       </c>
       <c r="J189" t="n">
-        <v>99.07527913276064</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="K189" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_17 kW</t>
+          <t>SH_OilBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B190" s="2" t="n">
@@ -7458,34 +7458,34 @@
         <v>0</v>
       </c>
       <c r="D190" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E190" t="n">
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
       </c>
       <c r="H190" t="n">
-        <v>111.3962236659374</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="I190" t="n">
         <v>0</v>
       </c>
       <c r="J190" t="n">
-        <v>111.3962236659374</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="K190" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_17 kW</t>
+          <t>SH_OilBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B191" s="2" t="n">
@@ -7495,34 +7495,34 @@
         <v>0</v>
       </c>
       <c r="D191" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E191" t="n">
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
       </c>
       <c r="H191" t="n">
-        <v>122.1272439602363</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="I191" t="n">
         <v>0</v>
       </c>
       <c r="J191" t="n">
-        <v>122.1272439602363</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="K191" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_80 kW</t>
+          <t>SH_PelletBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B192" s="2" t="n">
@@ -7532,34 +7532,34 @@
         <v>0</v>
       </c>
       <c r="D192" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E192" t="n">
         <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
       </c>
       <c r="H192" t="n">
-        <v>10.90087498351555</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="I192" t="n">
         <v>0</v>
       </c>
       <c r="J192" t="n">
-        <v>10.90087498351555</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K192" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_80 kW</t>
+          <t>SH_PelletBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B193" s="2" t="n">
@@ -7569,34 +7569,34 @@
         <v>0</v>
       </c>
       <c r="D193" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E193" t="n">
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
       </c>
       <c r="H193" t="n">
-        <v>12.19176658958502</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="I193" t="n">
         <v>0</v>
       </c>
       <c r="J193" t="n">
-        <v>12.19176658958502</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K193" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_80 kW</t>
+          <t>SH_PelletBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B194" s="2" t="n">
@@ -7606,34 +7606,34 @@
         <v>0</v>
       </c>
       <c r="D194" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E194" t="n">
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
       </c>
       <c r="H194" t="n">
-        <v>13.26038644430111</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="I194" t="n">
         <v>0</v>
       </c>
       <c r="J194" t="n">
-        <v>13.26038644430111</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K194" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_80 kW</t>
+          <t>SH_PelletBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B195" s="2" t="n">
@@ -7643,34 +7643,34 @@
         <v>0</v>
       </c>
       <c r="D195" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E195" t="n">
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
       </c>
       <c r="H195" t="n">
-        <v>14.1749555792428</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="I195" t="n">
         <v>0</v>
       </c>
       <c r="J195" t="n">
-        <v>14.1749555792428</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K195" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SH_PelletBoiler_s_80 kW</t>
+          <t>SH_PelletBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B196" s="2" t="n">
@@ -7680,145 +7680,145 @@
         <v>0</v>
       </c>
       <c r="D196" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E196" t="n">
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
       </c>
       <c r="H196" t="n">
-        <v>14.97150651908118</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="I196" t="n">
         <v>0</v>
       </c>
       <c r="J196" t="n">
-        <v>14.97150651908118</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K196" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_17 kW</t>
+          <t>SH_PelletBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B197" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C197" t="n">
-        <v>15.3189113449408</v>
+        <v>0</v>
       </c>
       <c r="D197" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E197" t="n">
-        <v>16.75287992575953</v>
+        <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="G197" t="n">
-        <v>17.81750751026624</v>
+        <v>0</v>
       </c>
       <c r="H197" t="n">
-        <v>67.28827832216861</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="I197" t="n">
-        <v>19.38671051669944</v>
+        <v>0</v>
       </c>
       <c r="J197" t="n">
-        <v>67.28827832216861</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="K197" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_17 kW</t>
+          <t>SH_PelletBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B198" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C198" t="n">
-        <v>15.3189113449408</v>
+        <v>0</v>
       </c>
       <c r="D198" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E198" t="n">
-        <v>16.75287992575953</v>
+        <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="G198" t="n">
-        <v>17.81750751026624</v>
+        <v>0</v>
       </c>
       <c r="H198" t="n">
-        <v>84.67898534372102</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="I198" t="n">
-        <v>19.38671051669944</v>
+        <v>0</v>
       </c>
       <c r="J198" t="n">
-        <v>84.67898534372102</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="K198" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_17 kW</t>
+          <t>SH_PelletBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B199" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C199" t="n">
-        <v>15.3189113449408</v>
+        <v>0</v>
       </c>
       <c r="D199" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E199" t="n">
-        <v>16.75287992575953</v>
+        <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="G199" t="n">
-        <v>17.81750751026624</v>
+        <v>0</v>
       </c>
       <c r="H199" t="n">
-        <v>99.07527913276064</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="I199" t="n">
-        <v>19.38671051669944</v>
+        <v>0</v>
       </c>
       <c r="J199" t="n">
-        <v>99.07527913276064</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="K199" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_17 kW</t>
+          <t>SH_PelletBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B200" s="2" t="n">
@@ -7828,34 +7828,34 @@
         <v>0</v>
       </c>
       <c r="D200" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E200" t="n">
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
       </c>
       <c r="H200" t="n">
-        <v>111.3962236659374</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="I200" t="n">
         <v>0</v>
       </c>
       <c r="J200" t="n">
-        <v>111.3962236659374</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="K200" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_17 kW</t>
+          <t>SH_PelletBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B201" s="2" t="n">
@@ -7865,145 +7865,145 @@
         <v>0</v>
       </c>
       <c r="D201" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E201" t="n">
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>1114.849449025352</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
       </c>
       <c r="H201" t="n">
-        <v>122.1272439602363</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="I201" t="n">
         <v>0</v>
       </c>
       <c r="J201" t="n">
-        <v>122.1272439602363</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="K201" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_80 kW</t>
+          <t>SH_WoodBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B202" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C202" t="n">
-        <v>0.1532993805737606</v>
+        <v>0.231221943401857</v>
       </c>
       <c r="D202" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E202" t="n">
-        <v>0.2634026619397222</v>
+        <v>0.2273339501006746</v>
       </c>
       <c r="F202" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="G202" t="n">
-        <v>0.2388391148870171</v>
+        <v>0.3081243457284324</v>
       </c>
       <c r="H202" t="n">
-        <v>10.90087498351555</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="I202" t="n">
-        <v>0.1726817292722427</v>
+        <v>0.2213826310353668</v>
       </c>
       <c r="J202" t="n">
-        <v>10.90087498351555</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K202" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_80 kW</t>
+          <t>SH_WoodBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B203" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C203" t="n">
-        <v>0.1532993805737606</v>
+        <v>0.231221943401857</v>
       </c>
       <c r="D203" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E203" t="n">
-        <v>0.2634026619397222</v>
+        <v>0.2273339501006746</v>
       </c>
       <c r="F203" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="G203" t="n">
-        <v>0.2388391148870171</v>
+        <v>0.3088627665563856</v>
       </c>
       <c r="H203" t="n">
-        <v>12.19176658958502</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="I203" t="n">
-        <v>0.1726817292722427</v>
+        <v>0.2213826310353668</v>
       </c>
       <c r="J203" t="n">
-        <v>12.19176658958502</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K203" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_80 kW</t>
+          <t>SH_WoodBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B204" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C204" t="n">
-        <v>0.1532993805737606</v>
+        <v>0.231221943401857</v>
       </c>
       <c r="D204" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E204" t="n">
-        <v>0.2634026619397222</v>
+        <v>0.2273339501006746</v>
       </c>
       <c r="F204" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="G204" t="n">
-        <v>0.2388391148870171</v>
+        <v>0.3088627665563856</v>
       </c>
       <c r="H204" t="n">
-        <v>13.26038644430111</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="I204" t="n">
-        <v>0.1726817292722427</v>
+        <v>0.2213826310353668</v>
       </c>
       <c r="J204" t="n">
-        <v>13.26038644430111</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K204" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_80 kW</t>
+          <t>SH_WoodBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B205" s="2" t="n">
@@ -8013,34 +8013,34 @@
         <v>0</v>
       </c>
       <c r="D205" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E205" t="n">
         <v>0</v>
       </c>
       <c r="F205" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="G205" t="n">
-        <v>0</v>
+        <v>0.000738420827953177</v>
       </c>
       <c r="H205" t="n">
-        <v>14.1749555792428</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="I205" t="n">
         <v>0</v>
       </c>
       <c r="J205" t="n">
-        <v>14.1749555792428</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K205" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SH_WoodBoiler_s_80 kW</t>
+          <t>SH_WoodBoiler_s_17 kW</t>
         </is>
       </c>
       <c r="B206" s="2" t="n">
@@ -8050,139 +8050,145 @@
         <v>0</v>
       </c>
       <c r="D206" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="E206" t="n">
         <v>0</v>
       </c>
       <c r="F206" t="n">
-        <v>88.66010124321591</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
       </c>
       <c r="H206" t="n">
-        <v>14.97150651908118</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="I206" t="n">
         <v>0</v>
       </c>
       <c r="J206" t="n">
-        <v>14.97150651908118</v>
+        <v>1114.849449025352</v>
       </c>
       <c r="K206" t="n">
-        <v>0.08</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>SH_roof_retrofit</t>
+          <t>SH_WoodBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B207" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C207" t="n">
-        <v>0</v>
+        <v>0.06477336234635866</v>
       </c>
       <c r="D207" t="n">
-        <v>8</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E207" t="n">
-        <v>0</v>
+        <v>0.1508128897330668</v>
       </c>
       <c r="F207" t="n">
-        <v>8</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="G207" t="n">
-        <v>0</v>
+        <v>0.1405231945109061</v>
       </c>
       <c r="H207" t="n">
-        <v>2.063590033441665</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="I207" t="n">
-        <v>0</v>
+        <v>0.1242408942663229</v>
       </c>
       <c r="J207" t="n">
-        <v>2.063590033441665</v>
-      </c>
-      <c r="K207" t="inlineStr"/>
+        <v>88.66010124321591</v>
+      </c>
+      <c r="K207" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SH_roof_retrofit</t>
+          <t>SH_WoodBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B208" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="C208" t="n">
-        <v>0</v>
+        <v>0.06477336234635866</v>
       </c>
       <c r="D208" t="n">
-        <v>8</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E208" t="n">
-        <v>0</v>
+        <v>0.1508128897330668</v>
       </c>
       <c r="F208" t="n">
-        <v>8</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="G208" t="n">
-        <v>0</v>
+        <v>0.1405231945109061</v>
       </c>
       <c r="H208" t="n">
-        <v>3.171170109772028</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="I208" t="n">
-        <v>0</v>
+        <v>0.1242408942663229</v>
       </c>
       <c r="J208" t="n">
-        <v>3.171170109772028</v>
-      </c>
-      <c r="K208" t="inlineStr"/>
+        <v>88.66010124321591</v>
+      </c>
+      <c r="K208" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SH_roof_retrofit</t>
+          <t>SH_WoodBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B209" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="C209" t="n">
-        <v>0</v>
+        <v>0.06477336234635866</v>
       </c>
       <c r="D209" t="n">
-        <v>8</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E209" t="n">
-        <v>0</v>
+        <v>0.1508128897330668</v>
       </c>
       <c r="F209" t="n">
-        <v>8</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="G209" t="n">
-        <v>0</v>
+        <v>0.1405231945109061</v>
       </c>
       <c r="H209" t="n">
-        <v>3.858013789308042</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="I209" t="n">
-        <v>0</v>
+        <v>0.1242408942663229</v>
       </c>
       <c r="J209" t="n">
-        <v>3.858013789308042</v>
-      </c>
-      <c r="K209" t="inlineStr"/>
+        <v>88.66010124321591</v>
+      </c>
+      <c r="K209" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>SH_roof_retrofit</t>
+          <t>SH_WoodBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B210" s="2" t="n">
@@ -8192,32 +8198,34 @@
         <v>0</v>
       </c>
       <c r="D210" t="n">
-        <v>8</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E210" t="n">
         <v>0</v>
       </c>
       <c r="F210" t="n">
-        <v>8</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
       </c>
       <c r="H210" t="n">
-        <v>4.328245840125561</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="I210" t="n">
         <v>0</v>
       </c>
       <c r="J210" t="n">
-        <v>4.328245840125561</v>
-      </c>
-      <c r="K210" t="inlineStr"/>
+        <v>88.66010124321591</v>
+      </c>
+      <c r="K210" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>SH_roof_retrofit</t>
+          <t>SH_WoodBoiler_s_80 kW</t>
         </is>
       </c>
       <c r="B211" s="2" t="n">
@@ -8227,32 +8235,34 @@
         <v>0</v>
       </c>
       <c r="D211" t="n">
-        <v>8</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="E211" t="n">
         <v>0</v>
       </c>
       <c r="F211" t="n">
-        <v>8</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
       </c>
       <c r="H211" t="n">
-        <v>4.674107536912043</v>
+        <v>88.66010124321591</v>
       </c>
       <c r="I211" t="n">
         <v>0</v>
       </c>
       <c r="J211" t="n">
-        <v>4.674107536912043</v>
-      </c>
-      <c r="K211" t="inlineStr"/>
+        <v>88.66010124321591</v>
+      </c>
+      <c r="K211" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>SH_wall_retrofit</t>
+          <t>SH_roof_retrofit</t>
         </is>
       </c>
       <c r="B212" s="2" t="n">
@@ -8268,7 +8278,7 @@
         <v>0</v>
       </c>
       <c r="F212" t="n">
-        <v>8</v>
+        <v>2.063590033441665</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -8280,14 +8290,14 @@
         <v>0</v>
       </c>
       <c r="J212" t="n">
-        <v>2.063590033441665</v>
+        <v>8</v>
       </c>
       <c r="K212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>SH_wall_retrofit</t>
+          <t>SH_roof_retrofit</t>
         </is>
       </c>
       <c r="B213" s="2" t="n">
@@ -8303,7 +8313,7 @@
         <v>0</v>
       </c>
       <c r="F213" t="n">
-        <v>8</v>
+        <v>3.171170109772028</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -8315,14 +8325,14 @@
         <v>0</v>
       </c>
       <c r="J213" t="n">
-        <v>3.171170109772028</v>
+        <v>8</v>
       </c>
       <c r="K213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>SH_wall_retrofit</t>
+          <t>SH_roof_retrofit</t>
         </is>
       </c>
       <c r="B214" s="2" t="n">
@@ -8338,7 +8348,7 @@
         <v>0</v>
       </c>
       <c r="F214" t="n">
-        <v>8</v>
+        <v>3.858013789308042</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -8350,14 +8360,14 @@
         <v>0</v>
       </c>
       <c r="J214" t="n">
-        <v>3.858013789308042</v>
+        <v>8</v>
       </c>
       <c r="K214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>SH_wall_retrofit</t>
+          <t>SH_roof_retrofit</t>
         </is>
       </c>
       <c r="B215" s="2" t="n">
@@ -8373,7 +8383,7 @@
         <v>0</v>
       </c>
       <c r="F215" t="n">
-        <v>8</v>
+        <v>4.328245840125561</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -8385,14 +8395,14 @@
         <v>0</v>
       </c>
       <c r="J215" t="n">
-        <v>4.328245840125561</v>
+        <v>8</v>
       </c>
       <c r="K215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>SH_wall_retrofit</t>
+          <t>SH_roof_retrofit</t>
         </is>
       </c>
       <c r="B216" s="2" t="n">
@@ -8408,7 +8418,7 @@
         <v>0</v>
       </c>
       <c r="F216" t="n">
-        <v>8</v>
+        <v>4.674107536912043</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -8420,14 +8430,14 @@
         <v>0</v>
       </c>
       <c r="J216" t="n">
-        <v>4.674107536912043</v>
+        <v>8</v>
       </c>
       <c r="K216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>SH_window_retrofit</t>
+          <t>SH_wall_retrofit</t>
         </is>
       </c>
       <c r="B217" s="2" t="n">
@@ -8443,7 +8453,7 @@
         <v>0</v>
       </c>
       <c r="F217" t="n">
-        <v>8</v>
+        <v>2.063590033441665</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -8455,14 +8465,14 @@
         <v>0</v>
       </c>
       <c r="J217" t="n">
-        <v>2.063590033441665</v>
+        <v>8</v>
       </c>
       <c r="K217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>SH_window_retrofit</t>
+          <t>SH_wall_retrofit</t>
         </is>
       </c>
       <c r="B218" s="2" t="n">
@@ -8478,7 +8488,7 @@
         <v>0</v>
       </c>
       <c r="F218" t="n">
-        <v>8</v>
+        <v>3.171170109772028</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -8490,14 +8500,14 @@
         <v>0</v>
       </c>
       <c r="J218" t="n">
-        <v>3.171170109772028</v>
+        <v>8</v>
       </c>
       <c r="K218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>SH_window_retrofit</t>
+          <t>SH_wall_retrofit</t>
         </is>
       </c>
       <c r="B219" s="2" t="n">
@@ -8513,7 +8523,7 @@
         <v>0</v>
       </c>
       <c r="F219" t="n">
-        <v>8</v>
+        <v>3.858013789308042</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -8525,14 +8535,14 @@
         <v>0</v>
       </c>
       <c r="J219" t="n">
-        <v>3.858013789308042</v>
+        <v>8</v>
       </c>
       <c r="K219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>SH_window_retrofit</t>
+          <t>SH_wall_retrofit</t>
         </is>
       </c>
       <c r="B220" s="2" t="n">
@@ -8548,7 +8558,7 @@
         <v>0</v>
       </c>
       <c r="F220" t="n">
-        <v>8</v>
+        <v>4.328245840125561</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -8560,14 +8570,14 @@
         <v>0</v>
       </c>
       <c r="J220" t="n">
-        <v>4.328245840125561</v>
+        <v>8</v>
       </c>
       <c r="K220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>SH_window_retrofit</t>
+          <t>SH_wall_retrofit</t>
         </is>
       </c>
       <c r="B221" s="2" t="n">
@@ -8583,7 +8593,7 @@
         <v>0</v>
       </c>
       <c r="F221" t="n">
-        <v>8</v>
+        <v>4.674107536912043</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -8595,9 +8605,184 @@
         <v>0</v>
       </c>
       <c r="J221" t="n">
+        <v>8</v>
+      </c>
+      <c r="K221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>SH_window_retrofit</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C222" t="n">
+        <v>0</v>
+      </c>
+      <c r="D222" t="n">
+        <v>8</v>
+      </c>
+      <c r="E222" t="n">
+        <v>0</v>
+      </c>
+      <c r="F222" t="n">
+        <v>2.063590033441665</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" t="n">
+        <v>2.063590033441665</v>
+      </c>
+      <c r="I222" t="n">
+        <v>0</v>
+      </c>
+      <c r="J222" t="n">
+        <v>8</v>
+      </c>
+      <c r="K222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>SH_window_retrofit</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="n">
+        <v>47849</v>
+      </c>
+      <c r="C223" t="n">
+        <v>0</v>
+      </c>
+      <c r="D223" t="n">
+        <v>8</v>
+      </c>
+      <c r="E223" t="n">
+        <v>0</v>
+      </c>
+      <c r="F223" t="n">
+        <v>3.171170109772028</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" t="n">
+        <v>3.171170109772028</v>
+      </c>
+      <c r="I223" t="n">
+        <v>0</v>
+      </c>
+      <c r="J223" t="n">
+        <v>8</v>
+      </c>
+      <c r="K223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>SH_window_retrofit</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="n">
+        <v>49675</v>
+      </c>
+      <c r="C224" t="n">
+        <v>0</v>
+      </c>
+      <c r="D224" t="n">
+        <v>8</v>
+      </c>
+      <c r="E224" t="n">
+        <v>0</v>
+      </c>
+      <c r="F224" t="n">
+        <v>3.858013789308042</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" t="n">
+        <v>3.858013789308042</v>
+      </c>
+      <c r="I224" t="n">
+        <v>0</v>
+      </c>
+      <c r="J224" t="n">
+        <v>8</v>
+      </c>
+      <c r="K224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>SH_window_retrofit</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="n">
+        <v>51502</v>
+      </c>
+      <c r="C225" t="n">
+        <v>0</v>
+      </c>
+      <c r="D225" t="n">
+        <v>8</v>
+      </c>
+      <c r="E225" t="n">
+        <v>0</v>
+      </c>
+      <c r="F225" t="n">
+        <v>4.328245840125561</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+      <c r="H225" t="n">
+        <v>4.328245840125561</v>
+      </c>
+      <c r="I225" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" t="n">
+        <v>8</v>
+      </c>
+      <c r="K225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>SH_window_retrofit</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="n">
+        <v>53328</v>
+      </c>
+      <c r="C226" t="n">
+        <v>0</v>
+      </c>
+      <c r="D226" t="n">
+        <v>8</v>
+      </c>
+      <c r="E226" t="n">
+        <v>0</v>
+      </c>
+      <c r="F226" t="n">
         <v>4.674107536912043</v>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" t="n">
+        <v>4.674107536912043</v>
+      </c>
+      <c r="I226" t="n">
+        <v>0</v>
+      </c>
+      <c r="J226" t="n">
+        <v>8</v>
+      </c>
+      <c r="K226" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
